--- a/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E2CE01-928C-4328-B619-BC83729A9983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA0FDD7-99C4-412B-AA97-67288F7E559C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="740">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -2252,6 +2252,9 @@
   </si>
   <si>
     <t>45301-9811038-3</t>
+  </si>
+  <si>
+    <t>0346-2628575</t>
   </si>
 </sst>
 </file>
@@ -2261,12 +2264,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2478,75 +2488,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2643,86 +2644,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -2920,25 +2841,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="35"/>
-      <tableStyleElement type="headerRow" dxfId="34"/>
-      <tableStyleElement type="totalRow" dxfId="33"/>
-      <tableStyleElement type="firstColumn" dxfId="32"/>
-      <tableStyleElement type="lastColumn" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
+      <tableStyleElement type="wholeTable" dxfId="26"/>
+      <tableStyleElement type="headerRow" dxfId="25"/>
+      <tableStyleElement type="totalRow" dxfId="24"/>
+      <tableStyleElement type="firstColumn" dxfId="23"/>
+      <tableStyleElement type="lastColumn" dxfId="22"/>
+      <tableStyleElement type="firstRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="28"/>
-      <tableStyleElement type="totalRow" dxfId="27"/>
-      <tableStyleElement type="firstRowStripe" dxfId="26"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="25"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="24"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="23"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="22"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="21"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="20"/>
-      <tableStyleElement type="pageFieldValues" dxfId="19"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="totalRow" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="13"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="12"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="11"/>
+      <tableStyleElement type="pageFieldValues" dxfId="10"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3231,22 +3152,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
     </row>
     <row r="2" spans="1:14" s="11" customFormat="1" ht="15.75">
       <c r="A2" s="8" t="s">
@@ -5573,7 +5494,9 @@
       <c r="L57" s="18" t="s">
         <v>609</v>
       </c>
-      <c r="M57" s="18"/>
+      <c r="M57" s="35" t="s">
+        <v>739</v>
+      </c>
       <c r="N57" s="7" t="s">
         <v>21</v>
       </c>
@@ -6574,7 +6497,9 @@
       <c r="K81" s="25">
         <v>45519</v>
       </c>
-      <c r="L81" s="18"/>
+      <c r="L81" s="35" t="s">
+        <v>570</v>
+      </c>
       <c r="M81" s="30" t="s">
         <v>712</v>
       </c>
@@ -12484,7 +12409,7 @@
       <c r="K224" s="25">
         <v>44842</v>
       </c>
-      <c r="L224" s="33" t="s">
+      <c r="L224" s="32" t="s">
         <v>69</v>
       </c>
       <c r="M224" s="7" t="s">
@@ -12525,7 +12450,7 @@
       <c r="J225" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K225" s="34">
+      <c r="K225" s="33">
         <v>44783</v>
       </c>
       <c r="L225" s="18" t="s">
@@ -12734,7 +12659,7 @@
       <c r="K230" s="25">
         <v>44124</v>
       </c>
-      <c r="L230" s="33" t="s">
+      <c r="L230" s="32" t="s">
         <v>727</v>
       </c>
       <c r="M230" s="18"/>
@@ -13534,7 +13459,7 @@
       <c r="K250" s="25">
         <v>44783</v>
       </c>
-      <c r="L250" s="33" t="s">
+      <c r="L250" s="32" t="s">
         <v>735</v>
       </c>
       <c r="M250" s="18"/>
@@ -14356,35 +14281,35 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C54:C84">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85:C108">
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C109">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C110:C141">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C142:C165">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218:C246">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C247:C272">
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C5268D-A220-429B-A66E-F6FE6F4C5426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF1BE07-30D6-4A04-897A-69C2712E0893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2598" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="795">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -1252,9 +1252,6 @@
     <t>Rubab Zahra</t>
   </si>
   <si>
-    <t>Saba Jamali</t>
-  </si>
-  <si>
     <t>Sajid Ali</t>
   </si>
   <si>
@@ -1429,9 +1426,6 @@
     <t>Ali Ejaz</t>
   </si>
   <si>
-    <t>Arbab Ali</t>
-  </si>
-  <si>
     <t>Azan</t>
   </si>
   <si>
@@ -1564,9 +1558,6 @@
     <t>Shafia</t>
   </si>
   <si>
-    <t>Meer Muhammad</t>
-  </si>
-  <si>
     <t>Sawebia</t>
   </si>
   <si>
@@ -1777,9 +1768,6 @@
     <t>0317-2891322</t>
   </si>
   <si>
-    <t>0310-156889</t>
-  </si>
-  <si>
     <t>43601-4360208-5</t>
   </si>
   <si>
@@ -2002,9 +1990,6 @@
     <t>43102-2776954-5</t>
   </si>
   <si>
-    <t>0318-6399790</t>
-  </si>
-  <si>
     <t>45202-2778329-3</t>
   </si>
   <si>
@@ -2317,13 +2302,124 @@
     <t>45202-0196680-2</t>
   </si>
   <si>
-    <t>43304-8272341-1</t>
-  </si>
-  <si>
     <t>42501-1443389-5</t>
   </si>
   <si>
-    <t>45504-5950388-5</t>
+    <t>0319-8352350</t>
+  </si>
+  <si>
+    <t>0300-2625466</t>
+  </si>
+  <si>
+    <t>0301-2073495</t>
+  </si>
+  <si>
+    <t>0307-2951807</t>
+  </si>
+  <si>
+    <t>0300-2950556</t>
+  </si>
+  <si>
+    <t>0303-3654783</t>
+  </si>
+  <si>
+    <t>43205-8599869-5</t>
+  </si>
+  <si>
+    <t>0310-0553389</t>
+  </si>
+  <si>
+    <t>0330-1243570</t>
+  </si>
+  <si>
+    <t>43301-2613778-1</t>
+  </si>
+  <si>
+    <t>0317-2800970</t>
+  </si>
+  <si>
+    <t>45202-2081370-5</t>
+  </si>
+  <si>
+    <t>0313-1163459</t>
+  </si>
+  <si>
+    <t>0333-2644782</t>
+  </si>
+  <si>
+    <t>0346-2216611</t>
+  </si>
+  <si>
+    <t>0315-3608569</t>
+  </si>
+  <si>
+    <t>0308-2742545</t>
+  </si>
+  <si>
+    <t>0307-2886358</t>
+  </si>
+  <si>
+    <t>0321-3522748</t>
+  </si>
+  <si>
+    <t>42201-561347-6</t>
+  </si>
+  <si>
+    <t>0342-2269168</t>
+  </si>
+  <si>
+    <t>0312-0119634</t>
+  </si>
+  <si>
+    <t>0304-2664842</t>
+  </si>
+  <si>
+    <t>0300-3247731</t>
+  </si>
+  <si>
+    <t>0306-2144122</t>
+  </si>
+  <si>
+    <t>0332-4231099</t>
+  </si>
+  <si>
+    <t>0310-1048803</t>
+  </si>
+  <si>
+    <t>0315-3021726</t>
+  </si>
+  <si>
+    <t>0310-2816124</t>
+  </si>
+  <si>
+    <t>0302-2643659</t>
+  </si>
+  <si>
+    <t>0333-3644117</t>
+  </si>
+  <si>
+    <t>0315-1274592</t>
+  </si>
+  <si>
+    <t>0303-2264365</t>
+  </si>
+  <si>
+    <t>0326-2208386</t>
+  </si>
+  <si>
+    <t>0300-2313665</t>
+  </si>
+  <si>
+    <t>0300-2317603</t>
+  </si>
+  <si>
+    <t>Sooha Jamali</t>
+  </si>
+  <si>
+    <t>0336-8603595</t>
+  </si>
+  <si>
+    <t>0313-2926917</t>
   </si>
 </sst>
 </file>
@@ -2333,12 +2429,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2453,7 +2563,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2463,6 +2573,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2564,62 +2680,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2630,7 +2761,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -2640,7 +2771,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -3229,22 +3360,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
     </row>
     <row r="2" spans="1:14" s="11" customFormat="1" ht="15.75">
       <c r="A2" s="8" t="s">
@@ -3290,295 +3421,295 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A3" s="18">
+    <row r="3" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="F3" s="18" t="s">
+      <c r="E3" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="F3" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="43">
         <v>42839</v>
       </c>
-      <c r="I3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="5">
+      <c r="I3" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="43">
         <v>45142</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="45" t="s">
+        <v>528</v>
+      </c>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A4" s="39">
+        <v>2</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="44"/>
+      <c r="D4" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="43">
+        <v>44355</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="43">
+        <v>45142</v>
+      </c>
+      <c r="L4" s="45" t="s">
+        <v>399</v>
+      </c>
+      <c r="M4" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="N4" s="45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A5" s="39">
+        <v>3</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="43">
+        <v>43478</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="43">
+        <v>45144</v>
+      </c>
+      <c r="L5" s="45" t="s">
+        <v>530</v>
+      </c>
+      <c r="M5" s="45" t="s">
         <v>531</v>
       </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A4" s="18">
-        <v>2</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="N5" s="45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A6" s="39">
+        <v>4</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="43">
+        <v>43807</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="43">
+        <v>45505</v>
+      </c>
+      <c r="L6" s="45" t="s">
+        <v>532</v>
+      </c>
+      <c r="M6" s="45" t="s">
+        <v>533</v>
+      </c>
+      <c r="N6" s="45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A7" s="39">
+        <v>5</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="44"/>
+      <c r="D7" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G7" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="5">
-        <v>44355</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="5">
-        <v>45142</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="N4" s="7" t="s">
+      <c r="H7" s="43">
+        <v>44197</v>
+      </c>
+      <c r="I7" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="43">
+        <v>45505</v>
+      </c>
+      <c r="L7" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="M7" s="45" t="s">
+        <v>534</v>
+      </c>
+      <c r="N7" s="45" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A5" s="18">
-        <v>3</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="18" t="s">
+    <row r="8" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A8" s="39">
+        <v>6</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G8" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="5">
-        <v>43478</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="5">
-        <v>45144</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A6" s="18">
-        <v>4</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="H8" s="43">
+        <v>44185</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="43">
+        <v>45505</v>
+      </c>
+      <c r="L8" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="M8" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="N8" s="45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="46" customFormat="1" ht="15.75">
+      <c r="A9" s="39">
+        <v>7</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="5">
-        <v>43807</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="5">
+      <c r="H9" s="43">
+        <v>44102</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="43">
         <v>45505</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A7" s="18">
-        <v>5</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="5">
-        <v>44197</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="5">
-        <v>45505</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="M7" s="7" t="s">
+      <c r="L9" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="45" t="s">
         <v>537</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A8" s="18">
-        <v>6</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="5">
-        <v>44185</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="5">
-        <v>45505</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="11" customFormat="1" ht="15.75">
-      <c r="A9" s="18">
-        <v>7</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="5">
-        <v>44102</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="5">
-        <v>45505</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="45" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3615,10 +3746,10 @@
         <v>45505</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>21</v>
@@ -3660,7 +3791,7 @@
         <v>40</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>57</v>
@@ -3699,10 +3830,10 @@
         <v>45505</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>57</v>
@@ -3744,7 +3875,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>21</v>
@@ -3786,7 +3917,7 @@
         <v>48</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>21</v>
@@ -3828,7 +3959,7 @@
         <v>51</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>21</v>
@@ -3870,7 +4001,7 @@
         <v>269</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="N16" s="7" t="s">
         <v>57</v>
@@ -3912,7 +4043,7 @@
         <v>56</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>57</v>
@@ -3954,7 +4085,7 @@
         <v>60</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>21</v>
@@ -3996,7 +4127,7 @@
         <v>63</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>57</v>
@@ -4038,7 +4169,7 @@
         <v>66</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="N20" s="7" t="s">
         <v>57</v>
@@ -4080,7 +4211,7 @@
         <v>69</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>57</v>
@@ -4122,7 +4253,7 @@
         <v>186</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>57</v>
@@ -4164,7 +4295,7 @@
         <v>74</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>21</v>
@@ -4203,10 +4334,10 @@
         <v>45505</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N24" s="7" t="s">
         <v>21</v>
@@ -4248,7 +4379,7 @@
         <v>79</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>21</v>
@@ -4287,10 +4418,10 @@
         <v>45505</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="N26" s="7" t="s">
         <v>21</v>
@@ -4329,10 +4460,10 @@
         <v>45505</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>21</v>
@@ -4371,10 +4502,10 @@
         <v>45505</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="N28" s="7" t="s">
         <v>21</v>
@@ -4413,10 +4544,10 @@
         <v>45505</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>21</v>
@@ -4455,10 +4586,10 @@
         <v>45505</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N30" s="7" t="s">
         <v>21</v>
@@ -4584,7 +4715,7 @@
         <v>95</v>
       </c>
       <c r="M33" s="18" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>57</v>
@@ -4626,7 +4757,7 @@
         <v>98</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="N34" s="7" t="s">
         <v>21</v>
@@ -4668,7 +4799,7 @@
         <v>101</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="N35" s="7" t="s">
         <v>57</v>
@@ -4710,7 +4841,7 @@
         <v>104</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="N36" s="7" t="s">
         <v>21</v>
@@ -4725,7 +4856,7 @@
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="14" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>105</v>
@@ -4749,10 +4880,10 @@
         <v>45535</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N37" s="7" t="s">
         <v>21</v>
@@ -4791,7 +4922,7 @@
         <v>45527</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7" t="s">
@@ -4810,7 +4941,7 @@
         <v>108</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>24</v>
@@ -4831,7 +4962,7 @@
         <v>45527</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7" t="s">
@@ -4871,10 +5002,10 @@
         <v>45505</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>21</v>
@@ -4913,10 +5044,10 @@
         <v>45505</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>580</v>
+        <v>416</v>
+      </c>
+      <c r="M41" s="36" t="s">
+        <v>781</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>57</v>
@@ -4955,10 +5086,10 @@
         <v>45505</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="N42" s="7" t="s">
         <v>21</v>
@@ -4997,10 +5128,10 @@
         <v>45535</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="N43" s="7" t="s">
         <v>21</v>
@@ -5039,10 +5170,10 @@
         <v>45505</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="N44" s="7" t="s">
         <v>21</v>
@@ -5084,7 +5215,7 @@
         <v>121</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N45" s="7" t="s">
         <v>57</v>
@@ -5123,10 +5254,10 @@
         <v>45505</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="N46" s="7" t="s">
         <v>21</v>
@@ -5141,7 +5272,7 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="14" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>124</v>
@@ -5163,10 +5294,10 @@
         <v>45551</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>21</v>
@@ -5208,7 +5339,7 @@
         <v>127</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="N48" s="7" t="s">
         <v>21</v>
@@ -5226,7 +5357,7 @@
         <v>128</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>24</v>
@@ -5245,10 +5376,10 @@
         <v>45559</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>21</v>
@@ -5290,7 +5421,7 @@
         <v>131</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>21</v>
@@ -5329,7 +5460,7 @@
         <v>45562</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7" t="s">
@@ -5345,10 +5476,10 @@
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="18" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
@@ -5369,10 +5500,10 @@
         <v>45569</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="N52" s="7" t="s">
         <v>21</v>
@@ -5454,7 +5585,7 @@
         <v>140</v>
       </c>
       <c r="M54" s="18" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N54" s="7" t="s">
         <v>21</v>
@@ -5494,7 +5625,7 @@
         <v>143</v>
       </c>
       <c r="M55" s="18" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>57</v>
@@ -5533,10 +5664,10 @@
         <v>45139</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="M56" s="33" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="N56" s="7" t="s">
         <v>21</v>
@@ -5578,7 +5709,7 @@
         <v>148</v>
       </c>
       <c r="M57" s="18" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="N57" s="7" t="s">
         <v>21</v>
@@ -5620,7 +5751,7 @@
         <v>150</v>
       </c>
       <c r="M58" s="18" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="N58" s="18" t="s">
         <v>57</v>
@@ -5638,7 +5769,7 @@
         <v>151</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>24</v>
@@ -5662,7 +5793,7 @@
         <v>152</v>
       </c>
       <c r="M59" s="18" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="N59" s="7" t="s">
         <v>21</v>
@@ -5704,7 +5835,7 @@
         <v>154</v>
       </c>
       <c r="M60" s="18" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="N60" s="18" t="s">
         <v>57</v>
@@ -5746,7 +5877,7 @@
         <v>157</v>
       </c>
       <c r="M61" s="18" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>21</v>
@@ -5788,7 +5919,7 @@
         <v>160</v>
       </c>
       <c r="M62" s="18" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="N62" s="7" t="s">
         <v>21</v>
@@ -5830,7 +5961,7 @@
         <v>163</v>
       </c>
       <c r="M63" s="18" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="N63" s="18" t="s">
         <v>57</v>
@@ -5872,7 +6003,7 @@
         <v>166</v>
       </c>
       <c r="M64" s="18" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="N64" s="18" t="s">
         <v>57</v>
@@ -5914,7 +6045,7 @@
         <v>169</v>
       </c>
       <c r="M65" s="18" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="N65" s="7" t="s">
         <v>21</v>
@@ -5998,7 +6129,7 @@
         <v>175</v>
       </c>
       <c r="M67" s="18" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N67" s="7" t="s">
         <v>57</v>
@@ -6040,7 +6171,7 @@
         <v>178</v>
       </c>
       <c r="M68" s="18" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N68" s="7" t="s">
         <v>21</v>
@@ -6082,7 +6213,7 @@
         <v>181</v>
       </c>
       <c r="M69" s="18" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N69" s="7" t="s">
         <v>21</v>
@@ -6124,7 +6255,7 @@
         <v>184</v>
       </c>
       <c r="M70" s="18" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="N70" s="18" t="s">
         <v>57</v>
@@ -6166,7 +6297,7 @@
         <v>186</v>
       </c>
       <c r="M71" s="18" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="N71" s="7" t="s">
         <v>57</v>
@@ -6208,7 +6339,7 @@
         <v>189</v>
       </c>
       <c r="M72" s="18" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="N72" s="7" t="s">
         <v>21</v>
@@ -6250,7 +6381,7 @@
         <v>191</v>
       </c>
       <c r="M73" s="18" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N73" s="7" t="s">
         <v>21</v>
@@ -6292,7 +6423,7 @@
         <v>194</v>
       </c>
       <c r="M74" s="18" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="N74" s="7" t="s">
         <v>21</v>
@@ -6334,7 +6465,7 @@
         <v>95</v>
       </c>
       <c r="M75" s="18" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="N75" s="7" t="s">
         <v>57</v>
@@ -6376,7 +6507,7 @@
         <v>198</v>
       </c>
       <c r="M76" s="18" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="N76" s="7" t="s">
         <v>57</v>
@@ -6418,7 +6549,7 @@
         <v>198</v>
       </c>
       <c r="M77" s="18" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="N77" s="7" t="s">
         <v>57</v>
@@ -6460,7 +6591,7 @@
         <v>35</v>
       </c>
       <c r="M78" s="18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N78" s="7" t="s">
         <v>57</v>
@@ -6475,7 +6606,7 @@
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="14" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E79" s="15" t="s">
         <v>201</v>
@@ -6502,7 +6633,7 @@
         <v>35</v>
       </c>
       <c r="M79" s="18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N79" s="7" t="s">
         <v>57</v>
@@ -6539,10 +6670,10 @@
         <v>45519</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M80" s="30" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="N80" s="7" t="s">
         <v>21</v>
@@ -6560,7 +6691,7 @@
         <v>203</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>24</v>
@@ -6584,7 +6715,7 @@
         <v>204</v>
       </c>
       <c r="M81" s="30" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="N81" s="7" t="s">
         <v>21</v>
@@ -6602,7 +6733,7 @@
         <v>205</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>24</v>
@@ -6623,10 +6754,10 @@
         <v>45519</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="M82" s="18" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="N82" s="7" t="s">
         <v>21</v>
@@ -6644,7 +6775,7 @@
         <v>209</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>24</v>
@@ -6665,10 +6796,10 @@
         <v>45537</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="M83" s="18" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="N83" s="7" t="s">
         <v>21</v>
@@ -6710,7 +6841,7 @@
         <v>212</v>
       </c>
       <c r="M84" s="30" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="N84" s="7" t="s">
         <v>21</v>
@@ -6794,7 +6925,7 @@
         <v>154</v>
       </c>
       <c r="M86" s="18" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="N86" s="18" t="s">
         <v>57</v>
@@ -6834,7 +6965,7 @@
         <v>220</v>
       </c>
       <c r="M87" s="18" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="N87" s="7" t="s">
         <v>21</v>
@@ -6876,7 +7007,7 @@
         <v>223</v>
       </c>
       <c r="M88" s="18" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="N88" s="18" t="s">
         <v>57</v>
@@ -6918,7 +7049,7 @@
         <v>226</v>
       </c>
       <c r="M89" s="18" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N89" s="18" t="s">
         <v>57</v>
@@ -6960,7 +7091,7 @@
         <v>229</v>
       </c>
       <c r="M90" s="18" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="N90" s="7" t="s">
         <v>21</v>
@@ -7002,7 +7133,7 @@
         <v>232</v>
       </c>
       <c r="M91" s="18" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="N91" s="7" t="s">
         <v>21</v>
@@ -7044,7 +7175,7 @@
         <v>166</v>
       </c>
       <c r="M92" s="18" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N92" s="18" t="s">
         <v>57</v>
@@ -7086,7 +7217,7 @@
         <v>236</v>
       </c>
       <c r="M93" s="18" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="N93" s="7" t="s">
         <v>21</v>
@@ -7128,7 +7259,7 @@
         <v>239</v>
       </c>
       <c r="M94" s="18" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="N94" s="7" t="s">
         <v>21</v>
@@ -7210,7 +7341,7 @@
         <v>244</v>
       </c>
       <c r="M96" s="18" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="N96" s="18" t="s">
         <v>57</v>
@@ -7252,7 +7383,7 @@
         <v>247</v>
       </c>
       <c r="M97" s="18" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="N97" s="7" t="s">
         <v>21</v>
@@ -7336,7 +7467,7 @@
         <v>226</v>
       </c>
       <c r="M99" s="18" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N99" s="7" t="s">
         <v>57</v>
@@ -7378,7 +7509,7 @@
         <v>253</v>
       </c>
       <c r="M100" s="18" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="N100" s="7" t="s">
         <v>21</v>
@@ -7420,7 +7551,7 @@
         <v>256</v>
       </c>
       <c r="M101" s="30" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="N101" s="7" t="s">
         <v>21</v>
@@ -7462,7 +7593,7 @@
         <v>259</v>
       </c>
       <c r="M102" s="18" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="N102" s="18" t="s">
         <v>57</v>
@@ -7504,7 +7635,7 @@
         <v>63</v>
       </c>
       <c r="M103" s="18" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="N103" s="7" t="s">
         <v>57</v>
@@ -7546,7 +7677,7 @@
         <v>66</v>
       </c>
       <c r="M104" s="18" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="N104" s="18" t="s">
         <v>57</v>
@@ -7588,7 +7719,7 @@
         <v>265</v>
       </c>
       <c r="M105" s="18" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="N105" s="7" t="s">
         <v>21</v>
@@ -7630,7 +7761,7 @@
         <v>223</v>
       </c>
       <c r="M106" s="18" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="N106" s="18" t="s">
         <v>57</v>
@@ -7672,7 +7803,7 @@
         <v>269</v>
       </c>
       <c r="M107" s="18" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="N107" s="7" t="s">
         <v>57</v>
@@ -7714,7 +7845,7 @@
         <v>208</v>
       </c>
       <c r="M108" s="18" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="N108" s="7" t="s">
         <v>21</v>
@@ -7756,7 +7887,7 @@
         <v>273</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="N109" s="7" t="s">
         <v>21</v>
@@ -7791,10 +7922,10 @@
       </c>
       <c r="K110" s="25"/>
       <c r="L110" s="7" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="M110" s="29" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="N110" s="7" t="s">
         <v>21</v>
@@ -7836,7 +7967,7 @@
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="29" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="N111" s="7" t="s">
         <v>21</v>
@@ -7875,10 +8006,10 @@
         <v>45240</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="M112" s="29" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="N112" s="7" t="s">
         <v>21</v>
@@ -7920,7 +8051,7 @@
         <v>215</v>
       </c>
       <c r="M113" s="29" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="N113" s="18" t="s">
         <v>57</v>
@@ -7962,7 +8093,7 @@
         <v>69</v>
       </c>
       <c r="M114" s="29" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="N114" s="7" t="s">
         <v>57</v>
@@ -8004,7 +8135,7 @@
         <v>150</v>
       </c>
       <c r="M115" s="29" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="N115" s="18" t="s">
         <v>57</v>
@@ -8039,7 +8170,7 @@
       </c>
       <c r="K116" s="25"/>
       <c r="L116" s="7"/>
-      <c r="M116" s="35"/>
+      <c r="M116" s="34"/>
       <c r="N116" s="7" t="s">
         <v>21</v>
       </c>
@@ -8080,7 +8211,7 @@
         <v>284</v>
       </c>
       <c r="M117" s="18" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="N117" s="7" t="s">
         <v>57</v>
@@ -8204,7 +8335,7 @@
         <v>294</v>
       </c>
       <c r="M120" s="29" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="N120" s="7" t="s">
         <v>21</v>
@@ -8246,7 +8377,7 @@
         <v>297</v>
       </c>
       <c r="M121" s="29" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="N121" s="7" t="s">
         <v>21</v>
@@ -8288,7 +8419,7 @@
         <v>300</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="N122" s="18" t="s">
         <v>57</v>
@@ -8330,7 +8461,7 @@
         <v>303</v>
       </c>
       <c r="M123" s="29" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="N123" s="18" t="s">
         <v>57</v>
@@ -8370,7 +8501,7 @@
       </c>
       <c r="L124" s="7"/>
       <c r="M124" s="29" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="N124" s="7" t="s">
         <v>21</v>
@@ -8412,7 +8543,7 @@
         <v>307</v>
       </c>
       <c r="M125" s="29" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="N125" s="18" t="s">
         <v>57</v>
@@ -8454,7 +8585,7 @@
         <v>300</v>
       </c>
       <c r="M126" s="29" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="N126" s="18" t="s">
         <v>57</v>
@@ -8536,7 +8667,7 @@
         <v>313</v>
       </c>
       <c r="M128" s="29" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="N128" s="7" t="s">
         <v>21</v>
@@ -8578,7 +8709,7 @@
         <v>316</v>
       </c>
       <c r="M129" s="18" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="N129" s="18" t="s">
         <v>57</v>
@@ -8614,7 +8745,7 @@
       <c r="K130" s="25"/>
       <c r="L130" s="7"/>
       <c r="M130" s="29" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="N130" s="7" t="s">
         <v>21</v>
@@ -8656,7 +8787,7 @@
         <v>259</v>
       </c>
       <c r="M131" s="29" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="N131" s="18" t="s">
         <v>57</v>
@@ -8739,7 +8870,9 @@
       <c r="L133" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="M133" s="18"/>
+      <c r="M133" s="36" t="s">
+        <v>692</v>
+      </c>
       <c r="N133" s="18" t="s">
         <v>57</v>
       </c>
@@ -8779,7 +8912,9 @@
       <c r="L134" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="M134" s="18"/>
+      <c r="M134" s="36" t="s">
+        <v>776</v>
+      </c>
       <c r="N134" s="7" t="s">
         <v>21</v>
       </c>
@@ -8820,7 +8955,7 @@
         <v>329</v>
       </c>
       <c r="M135" s="29" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="N135" s="7" t="s">
         <v>21</v>
@@ -8860,7 +8995,7 @@
         <v>332</v>
       </c>
       <c r="M136" s="29" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="N136" s="7" t="s">
         <v>21</v>
@@ -8942,7 +9077,7 @@
         <v>184</v>
       </c>
       <c r="M138" s="29" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="N138" s="18" t="s">
         <v>57</v>
@@ -8983,7 +9118,9 @@
       <c r="L139" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="M139" s="18"/>
+      <c r="M139" s="36" t="s">
+        <v>546</v>
+      </c>
       <c r="N139" s="7" t="s">
         <v>57</v>
       </c>
@@ -9064,7 +9201,7 @@
         <v>341</v>
       </c>
       <c r="M141" s="29" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="N141" s="7" t="s">
         <v>57</v>
@@ -9106,7 +9243,7 @@
         <v>344</v>
       </c>
       <c r="M142" s="29" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="N142" s="7" t="s">
         <v>21</v>
@@ -9148,7 +9285,7 @@
         <v>303</v>
       </c>
       <c r="M143" s="29" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="N143" s="18" t="s">
         <v>57</v>
@@ -9190,7 +9327,7 @@
         <v>347</v>
       </c>
       <c r="M144" s="29" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="N144" s="7" t="s">
         <v>21</v>
@@ -9272,7 +9409,7 @@
         <v>307</v>
       </c>
       <c r="M146" s="29" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="N146" s="18" t="s">
         <v>57</v>
@@ -9314,7 +9451,7 @@
         <v>244</v>
       </c>
       <c r="M147" s="29" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="N147" s="18" t="s">
         <v>57</v>
@@ -9356,7 +9493,7 @@
         <v>355</v>
       </c>
       <c r="M148" s="29" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="N148" s="7" t="s">
         <v>21</v>
@@ -9398,7 +9535,7 @@
         <v>358</v>
       </c>
       <c r="M149" s="29" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="N149" s="7" t="s">
         <v>21</v>
@@ -9440,7 +9577,7 @@
         <v>361</v>
       </c>
       <c r="M150" s="29" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="N150" s="7" t="s">
         <v>21</v>
@@ -9482,7 +9619,7 @@
         <v>323</v>
       </c>
       <c r="M151" s="29" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="N151" s="18" t="s">
         <v>57</v>
@@ -9563,7 +9700,9 @@
       <c r="L153" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="M153" s="18"/>
+      <c r="M153" s="36" t="s">
+        <v>785</v>
+      </c>
       <c r="N153" s="18" t="s">
         <v>57</v>
       </c>
@@ -9602,7 +9741,7 @@
         <v>369</v>
       </c>
       <c r="M154" s="29" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="N154" s="7" t="s">
         <v>21</v>
@@ -9682,7 +9821,7 @@
         <v>374</v>
       </c>
       <c r="M156" s="29" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="N156" s="7" t="s">
         <v>21</v>
@@ -9844,7 +9983,7 @@
         <v>383</v>
       </c>
       <c r="M160" s="18" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="N160" s="18" t="s">
         <v>57</v>
@@ -9886,7 +10025,7 @@
         <v>385</v>
       </c>
       <c r="M161" s="18" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="N161" s="7" t="s">
         <v>57</v>
@@ -9901,7 +10040,7 @@
       </c>
       <c r="C162" s="21"/>
       <c r="D162" s="14" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="E162" s="15" t="s">
         <v>386</v>
@@ -9925,10 +10064,10 @@
         <v>45523</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="M162" s="18" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="N162" s="7" t="s">
         <v>21</v>
@@ -9970,7 +10109,7 @@
         <v>389</v>
       </c>
       <c r="M163" s="29" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="N163" s="7" t="s">
         <v>21</v>
@@ -10012,7 +10151,7 @@
         <v>392</v>
       </c>
       <c r="M164" s="29" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="N164" s="7" t="s">
         <v>21</v>
@@ -10032,7 +10171,7 @@
         <v>393</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="F165" s="18" t="s">
         <v>17</v>
@@ -10053,10 +10192,10 @@
         <v>45223</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="M165" s="18" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="N165" s="7" t="s">
         <v>21</v>
@@ -10076,7 +10215,7 @@
         <v>395</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F166" s="18" t="s">
         <v>17</v>
@@ -10099,8 +10238,8 @@
       <c r="L166" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M166" s="35" t="s">
-        <v>736</v>
+      <c r="M166" s="34" t="s">
+        <v>731</v>
       </c>
       <c r="N166" s="7" t="s">
         <v>21</v>
@@ -10117,7 +10256,7 @@
         <v>523</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="E167" s="15" t="s">
         <v>360</v>
@@ -10141,7 +10280,9 @@
         <v>44440</v>
       </c>
       <c r="L167" s="7"/>
-      <c r="M167" s="18"/>
+      <c r="M167" s="36" t="s">
+        <v>782</v>
+      </c>
       <c r="N167" s="7" t="s">
         <v>21</v>
       </c>
@@ -10157,10 +10298,10 @@
         <v>668</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F168" s="18" t="s">
         <v>17</v>
@@ -10181,10 +10322,10 @@
         <v>45024</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="M168" s="18" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="N168" s="7" t="s">
         <v>57</v>
@@ -10225,10 +10366,10 @@
         <v>45140</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="M169" s="18" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="N169" s="7" t="s">
         <v>57</v>
@@ -10269,9 +10410,11 @@
         <v>45140</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="M170" s="18"/>
+        <v>701</v>
+      </c>
+      <c r="M170" s="36" t="s">
+        <v>784</v>
+      </c>
       <c r="N170" s="7" t="s">
         <v>21</v>
       </c>
@@ -10307,12 +10450,14 @@
       <c r="J171" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K171" s="25"/>
+      <c r="K171" s="25">
+        <v>45177</v>
+      </c>
       <c r="L171" s="7" t="s">
         <v>284</v>
       </c>
       <c r="M171" s="18" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="N171" s="7" t="s">
         <v>57</v>
@@ -10356,7 +10501,7 @@
         <v>60</v>
       </c>
       <c r="M172" s="18" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="N172" s="7" t="s">
         <v>57</v>
@@ -10376,7 +10521,7 @@
         <v>397</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F173" s="18" t="s">
         <v>17</v>
@@ -10394,12 +10539,14 @@
         <v>20</v>
       </c>
       <c r="K173" s="25">
-        <v>45227</v>
+        <v>45223</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="M173" s="18"/>
+        <v>732</v>
+      </c>
+      <c r="M173" s="36" t="s">
+        <v>783</v>
+      </c>
       <c r="N173" s="7" t="s">
         <v>21</v>
       </c>
@@ -10442,7 +10589,7 @@
         <v>399</v>
       </c>
       <c r="M174" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="N174" s="7" t="s">
         <v>57</v>
@@ -10483,10 +10630,10 @@
         <v>45140</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="M175" s="18" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="N175" s="7" t="s">
         <v>21</v>
@@ -10530,7 +10677,7 @@
         <v>101</v>
       </c>
       <c r="M176" s="18" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="N176" s="7" t="s">
         <v>57</v>
@@ -10571,10 +10718,10 @@
         <v>45153</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M177" s="18" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N177" s="7" t="s">
         <v>57</v>
@@ -10618,7 +10765,7 @@
         <v>316</v>
       </c>
       <c r="M178" s="18" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="N178" s="18" t="s">
         <v>57</v>
@@ -10662,7 +10809,7 @@
         <v>383</v>
       </c>
       <c r="M179" s="18" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="N179" s="18" t="s">
         <v>57</v>
@@ -10675,12 +10822,14 @@
       <c r="B180" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="20"/>
+      <c r="C180" s="20">
+        <v>522</v>
+      </c>
       <c r="D180" s="14" t="s">
+        <v>792</v>
+      </c>
+      <c r="E180" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="E180" s="15" t="s">
-        <v>406</v>
       </c>
       <c r="F180" s="18" t="s">
         <v>17</v>
@@ -10697,12 +10846,14 @@
       <c r="J180" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K180" s="25"/>
+      <c r="K180" s="25">
+        <v>44440</v>
+      </c>
       <c r="L180" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="M180" s="18" t="s">
-        <v>655</v>
+        <v>650</v>
+      </c>
+      <c r="M180" s="38" t="s">
+        <v>793</v>
       </c>
       <c r="N180" s="7" t="s">
         <v>21</v>
@@ -10719,7 +10870,7 @@
         <v>676</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E181" s="15" t="s">
         <v>225</v>
@@ -10743,9 +10894,11 @@
         <v>45146</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>738</v>
-      </c>
-      <c r="M181" s="18"/>
+        <v>733</v>
+      </c>
+      <c r="M181" s="38" t="s">
+        <v>610</v>
+      </c>
       <c r="N181" s="7" t="s">
         <v>21</v>
       </c>
@@ -10761,7 +10914,7 @@
         <v>654</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E182" s="15" t="s">
         <v>219</v>
@@ -10785,10 +10938,10 @@
         <v>45139</v>
       </c>
       <c r="L182" s="7" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="M182" s="18" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="N182" s="7" t="s">
         <v>21</v>
@@ -10805,7 +10958,7 @@
         <v>658</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E183" s="15" t="s">
         <v>222</v>
@@ -10829,9 +10982,11 @@
         <v>45140</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="M183" s="18"/>
+        <v>709</v>
+      </c>
+      <c r="M183" s="38" t="s">
+        <v>625</v>
+      </c>
       <c r="N183" s="7" t="s">
         <v>21</v>
       </c>
@@ -10871,10 +11026,10 @@
         <v>45303</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="M184" s="35" t="s">
-        <v>740</v>
+        <v>734</v>
+      </c>
+      <c r="M184" s="34" t="s">
+        <v>735</v>
       </c>
       <c r="N184" s="7" t="s">
         <v>21</v>
@@ -10891,10 +11046,10 @@
         <v>653</v>
       </c>
       <c r="D185" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="E185" s="15" t="s">
         <v>410</v>
-      </c>
-      <c r="E185" s="15" t="s">
-        <v>411</v>
       </c>
       <c r="F185" s="18" t="s">
         <v>17</v>
@@ -10915,10 +11070,10 @@
         <v>45139</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="M185" s="18" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="N185" s="7" t="s">
         <v>57</v>
@@ -10935,10 +11090,10 @@
         <v>660</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="F186" s="18" t="s">
         <v>17</v>
@@ -10959,10 +11114,10 @@
         <v>45140</v>
       </c>
       <c r="L186" s="7" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="M186" s="18" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="N186" s="7" t="s">
         <v>21</v>
@@ -10977,10 +11132,10 @@
       </c>
       <c r="C187" s="20"/>
       <c r="D187" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="E187" s="15" t="s">
         <v>413</v>
-      </c>
-      <c r="E187" s="15" t="s">
-        <v>414</v>
       </c>
       <c r="F187" s="18" t="s">
         <v>17</v>
@@ -10999,10 +11154,10 @@
       </c>
       <c r="K187" s="25"/>
       <c r="L187" s="7" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="M187" s="18" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="N187" s="7" t="s">
         <v>57</v>
@@ -11020,7 +11175,7 @@
         <v>390</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F188" s="18" t="s">
         <v>17</v>
@@ -11039,10 +11194,10 @@
       </c>
       <c r="K188" s="25"/>
       <c r="L188" s="7" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="M188" s="18" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="N188" s="7" t="s">
         <v>57</v>
@@ -11057,10 +11212,10 @@
       </c>
       <c r="C189" s="20"/>
       <c r="D189" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F189" s="18" t="s">
         <v>17</v>
@@ -11077,8 +11232,8 @@
       </c>
       <c r="K189" s="25"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="35" t="s">
-        <v>741</v>
+      <c r="M189" s="34" t="s">
+        <v>736</v>
       </c>
       <c r="N189" s="7" t="s">
         <v>21</v>
@@ -11118,7 +11273,7 @@
         <v>385</v>
       </c>
       <c r="M190" s="18" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="N190" s="7" t="s">
         <v>57</v>
@@ -11135,7 +11290,7 @@
         <v>784</v>
       </c>
       <c r="D191" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E191" s="15" t="s">
         <v>304</v>
@@ -11159,10 +11314,10 @@
         <v>45627</v>
       </c>
       <c r="L191" s="7" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="M191" s="18" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="N191" s="7" t="s">
         <v>21</v>
@@ -11182,7 +11337,7 @@
         <v>23</v>
       </c>
       <c r="E192" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F192" s="18" t="s">
         <v>24</v>
@@ -11203,9 +11358,11 @@
         <v>45153</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="M192" s="18"/>
+        <v>416</v>
+      </c>
+      <c r="M192" s="36" t="s">
+        <v>781</v>
+      </c>
       <c r="N192" s="7" t="s">
         <v>57</v>
       </c>
@@ -11221,7 +11378,7 @@
         <v>680</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E193" s="15" t="s">
         <v>180</v>
@@ -11244,8 +11401,12 @@
       <c r="K193" s="25">
         <v>45147</v>
       </c>
-      <c r="L193" s="7"/>
-      <c r="M193" s="18"/>
+      <c r="L193" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="M193" s="18" t="s">
+        <v>611</v>
+      </c>
       <c r="N193" s="7" t="s">
         <v>21</v>
       </c>
@@ -11264,7 +11425,7 @@
         <v>132</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F194" s="18" t="s">
         <v>24</v>
@@ -11285,10 +11446,10 @@
         <v>45139</v>
       </c>
       <c r="L194" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="M194" s="18" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="N194" s="7" t="s">
         <v>57</v>
@@ -11305,10 +11466,10 @@
         <v>670</v>
       </c>
       <c r="D195" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E195" s="15" t="s">
         <v>419</v>
-      </c>
-      <c r="E195" s="15" t="s">
-        <v>420</v>
       </c>
       <c r="F195" s="18" t="s">
         <v>24</v>
@@ -11329,10 +11490,10 @@
         <v>45142</v>
       </c>
       <c r="L195" s="7" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="M195" s="18" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="N195" s="7" t="s">
         <v>57</v>
@@ -11349,10 +11510,10 @@
         <v>683</v>
       </c>
       <c r="D196" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E196" s="15" t="s">
         <v>421</v>
-      </c>
-      <c r="E196" s="15" t="s">
-        <v>422</v>
       </c>
       <c r="F196" s="18" t="s">
         <v>24</v>
@@ -11373,9 +11534,11 @@
         <v>45148</v>
       </c>
       <c r="L196" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="M196" s="18"/>
+        <v>711</v>
+      </c>
+      <c r="M196" s="36" t="s">
+        <v>777</v>
+      </c>
       <c r="N196" s="7" t="s">
         <v>21</v>
       </c>
@@ -11391,10 +11554,10 @@
         <v>662</v>
       </c>
       <c r="D197" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="E197" s="15" t="s">
         <v>423</v>
-      </c>
-      <c r="E197" s="15" t="s">
-        <v>424</v>
       </c>
       <c r="F197" s="18" t="s">
         <v>24</v>
@@ -11415,9 +11578,11 @@
         <v>45140</v>
       </c>
       <c r="L197" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="M197" s="18"/>
+        <v>712</v>
+      </c>
+      <c r="M197" s="36" t="s">
+        <v>780</v>
+      </c>
       <c r="N197" s="7" t="s">
         <v>21</v>
       </c>
@@ -11433,7 +11598,7 @@
         <v>681</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E198" s="15" t="s">
         <v>76</v>
@@ -11457,9 +11622,11 @@
         <v>45148</v>
       </c>
       <c r="L198" s="7" t="s">
-        <v>742</v>
-      </c>
-      <c r="M198" s="18"/>
+        <v>737</v>
+      </c>
+      <c r="M198" s="36" t="s">
+        <v>778</v>
+      </c>
       <c r="N198" s="7" t="s">
         <v>21</v>
       </c>
@@ -11478,7 +11645,7 @@
         <v>123</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F199" s="18" t="s">
         <v>24</v>
@@ -11499,10 +11666,10 @@
         <v>45140</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="M199" s="18" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="N199" s="7" t="s">
         <v>21</v>
@@ -11519,7 +11686,7 @@
         <v>663</v>
       </c>
       <c r="D200" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E200" s="15" t="s">
         <v>73</v>
@@ -11543,7 +11710,7 @@
         <v>45140</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="M200" s="18"/>
       <c r="N200" s="7" t="s">
@@ -11561,7 +11728,7 @@
         <v>771</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E201" s="15" t="s">
         <v>283</v>
@@ -11585,13 +11752,13 @@
         <v>45223</v>
       </c>
       <c r="L201" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="M201" s="35" t="s">
-        <v>744</v>
+        <v>738</v>
+      </c>
+      <c r="M201" s="34" t="s">
+        <v>739</v>
       </c>
       <c r="N201" s="7" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202" spans="1:14" ht="15.75">
@@ -11629,11 +11796,13 @@
         <v>45223</v>
       </c>
       <c r="L202" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="M202" s="18"/>
+        <v>721</v>
+      </c>
+      <c r="M202" s="36" t="s">
+        <v>786</v>
+      </c>
       <c r="N202" s="7" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" spans="1:14" ht="15.75">
@@ -11647,10 +11816,10 @@
         <v>652</v>
       </c>
       <c r="D203" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="E203" s="15" t="s">
         <v>429</v>
-      </c>
-      <c r="E203" s="15" t="s">
-        <v>430</v>
       </c>
       <c r="F203" s="18" t="s">
         <v>24</v>
@@ -11671,10 +11840,10 @@
         <v>45139</v>
       </c>
       <c r="L203" s="7" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="M203" s="18" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="N203" s="7" t="s">
         <v>21</v>
@@ -11691,7 +11860,7 @@
         <v>682</v>
       </c>
       <c r="D204" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E204" s="15" t="s">
         <v>114</v>
@@ -11715,9 +11884,11 @@
         <v>45148</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="M204" s="18"/>
+        <v>740</v>
+      </c>
+      <c r="M204" s="36" t="s">
+        <v>613</v>
+      </c>
       <c r="N204" s="7" t="s">
         <v>21</v>
       </c>
@@ -11733,10 +11904,10 @@
         <v>775</v>
       </c>
       <c r="D205" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="E205" s="15" t="s">
         <v>432</v>
-      </c>
-      <c r="E205" s="15" t="s">
-        <v>433</v>
       </c>
       <c r="F205" s="18" t="s">
         <v>24</v>
@@ -11757,10 +11928,10 @@
         <v>45232</v>
       </c>
       <c r="L205" s="7" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="M205" s="33" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="N205" s="7" t="s">
         <v>21</v>
@@ -11777,7 +11948,7 @@
         <v>651</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E206" s="15" t="s">
         <v>142</v>
@@ -11804,7 +11975,7 @@
         <v>143</v>
       </c>
       <c r="M206" s="18" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="N206" s="7" t="s">
         <v>57</v>
@@ -11821,10 +11992,10 @@
         <v>678</v>
       </c>
       <c r="D207" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="E207" s="15" t="s">
         <v>435</v>
-      </c>
-      <c r="E207" s="15" t="s">
-        <v>436</v>
       </c>
       <c r="F207" s="18" t="s">
         <v>24</v>
@@ -11845,9 +12016,11 @@
         <v>44901</v>
       </c>
       <c r="L207" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="M207" s="18"/>
+        <v>436</v>
+      </c>
+      <c r="M207" s="36" t="s">
+        <v>671</v>
+      </c>
       <c r="N207" s="7" t="s">
         <v>21</v>
       </c>
@@ -11863,7 +12036,7 @@
         <v>674</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E208" s="15" t="s">
         <v>71</v>
@@ -11887,10 +12060,10 @@
         <v>45145</v>
       </c>
       <c r="L208" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="M208" s="35" t="s">
-        <v>747</v>
+        <v>741</v>
+      </c>
+      <c r="M208" s="34" t="s">
+        <v>742</v>
       </c>
       <c r="N208" s="7" t="s">
         <v>21</v>
@@ -11907,10 +12080,10 @@
         <v>666</v>
       </c>
       <c r="D209" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="E209" s="15" t="s">
         <v>439</v>
-      </c>
-      <c r="E209" s="15" t="s">
-        <v>440</v>
       </c>
       <c r="F209" s="18" t="s">
         <v>24</v>
@@ -11930,9 +12103,11 @@
       <c r="K209" s="25">
         <v>45140</v>
       </c>
-      <c r="L209" s="7"/>
-      <c r="M209" s="35" t="s">
-        <v>690</v>
+      <c r="L209" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="M209" s="34" t="s">
+        <v>685</v>
       </c>
       <c r="N209" s="7" t="s">
         <v>21</v>
@@ -11949,10 +12124,10 @@
         <v>786</v>
       </c>
       <c r="D210" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E210" s="15" t="s">
         <v>441</v>
-      </c>
-      <c r="E210" s="15" t="s">
-        <v>442</v>
       </c>
       <c r="F210" s="18" t="s">
         <v>24</v>
@@ -11973,10 +12148,10 @@
         <v>45303</v>
       </c>
       <c r="L210" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="M210" s="35" t="s">
-        <v>753</v>
+        <v>747</v>
+      </c>
+      <c r="M210" s="34" t="s">
+        <v>748</v>
       </c>
       <c r="N210" s="7" t="s">
         <v>21</v>
@@ -11993,10 +12168,10 @@
         <v>701</v>
       </c>
       <c r="D211" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="E211" s="15" t="s">
         <v>443</v>
-      </c>
-      <c r="E211" s="15" t="s">
-        <v>444</v>
       </c>
       <c r="F211" s="18" t="s">
         <v>24</v>
@@ -12017,9 +12192,11 @@
         <v>45153</v>
       </c>
       <c r="L211" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="M211" s="18"/>
+        <v>743</v>
+      </c>
+      <c r="M211" s="36" t="s">
+        <v>779</v>
+      </c>
       <c r="N211" s="7" t="s">
         <v>21</v>
       </c>
@@ -12038,7 +12215,7 @@
         <v>324</v>
       </c>
       <c r="E212" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F212" s="18" t="s">
         <v>24</v>
@@ -12059,9 +12236,11 @@
         <v>45142</v>
       </c>
       <c r="L212" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="M212" s="18"/>
+        <v>744</v>
+      </c>
+      <c r="M212" s="36" t="s">
+        <v>735</v>
+      </c>
       <c r="N212" s="7" t="s">
         <v>21</v>
       </c>
@@ -12077,10 +12256,10 @@
         <v>669</v>
       </c>
       <c r="D213" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="E213" s="15" t="s">
         <v>446</v>
-      </c>
-      <c r="E213" s="15" t="s">
-        <v>447</v>
       </c>
       <c r="F213" s="18" t="s">
         <v>24</v>
@@ -12101,7 +12280,7 @@
         <v>45142</v>
       </c>
       <c r="L213" s="7" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="M213" s="18"/>
       <c r="N213" s="7" t="s">
@@ -12119,10 +12298,10 @@
         <v>677</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E214" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F214" s="18" t="s">
         <v>24</v>
@@ -12143,10 +12322,10 @@
         <v>45146</v>
       </c>
       <c r="L214" s="7" t="s">
-        <v>752</v>
-      </c>
-      <c r="M214" s="35" t="s">
-        <v>753</v>
+        <v>747</v>
+      </c>
+      <c r="M214" s="34" t="s">
+        <v>748</v>
       </c>
       <c r="N214" s="7" t="s">
         <v>21</v>
@@ -12163,10 +12342,10 @@
         <v>783</v>
       </c>
       <c r="D215" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="E215" s="15" t="s">
         <v>449</v>
-      </c>
-      <c r="E215" s="15" t="s">
-        <v>450</v>
       </c>
       <c r="F215" s="18" t="s">
         <v>24</v>
@@ -12187,9 +12366,11 @@
         <v>45302</v>
       </c>
       <c r="L215" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="M215" s="18"/>
+        <v>746</v>
+      </c>
+      <c r="M215" s="36" t="s">
+        <v>774</v>
+      </c>
       <c r="N215" s="7" t="s">
         <v>21</v>
       </c>
@@ -12203,10 +12384,10 @@
       </c>
       <c r="C216" s="20"/>
       <c r="D216" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="E216" s="15" t="s">
         <v>451</v>
-      </c>
-      <c r="E216" s="15" t="s">
-        <v>452</v>
       </c>
       <c r="F216" s="18" t="s">
         <v>24</v>
@@ -12225,7 +12406,7 @@
       </c>
       <c r="K216" s="25"/>
       <c r="L216" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M216" s="18"/>
       <c r="N216" s="7" t="s">
@@ -12252,18 +12433,24 @@
         <v>24</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H217" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H217" s="25">
+        <v>41848</v>
+      </c>
       <c r="I217" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J217" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K217" s="25"/>
+      <c r="K217" s="25">
+        <v>44842</v>
+      </c>
       <c r="L217" s="7"/>
-      <c r="M217" s="18"/>
+      <c r="M217" s="36" t="s">
+        <v>756</v>
+      </c>
       <c r="N217" s="7" t="s">
         <v>21</v>
       </c>
@@ -12279,7 +12466,7 @@
         <v>646</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E218" s="15" t="s">
         <v>357</v>
@@ -12288,7 +12475,7 @@
         <v>24</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H218" s="25">
         <v>42975</v>
@@ -12306,7 +12493,7 @@
         <v>358</v>
       </c>
       <c r="M218" s="29" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="N218" s="7" t="s">
         <v>21</v>
@@ -12323,16 +12510,16 @@
         <v>690</v>
       </c>
       <c r="D219" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="E219" s="15" t="s">
         <v>456</v>
-      </c>
-      <c r="E219" s="15" t="s">
-        <v>457</v>
       </c>
       <c r="F219" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H219" s="25">
         <v>41879</v>
@@ -12346,8 +12533,12 @@
       <c r="K219" s="25">
         <v>45148</v>
       </c>
-      <c r="L219" s="7"/>
-      <c r="M219" s="18"/>
+      <c r="L219" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="M219" s="36" t="s">
+        <v>288</v>
+      </c>
       <c r="N219" s="7" t="s">
         <v>21</v>
       </c>
@@ -12363,7 +12554,7 @@
         <v>684</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E220" s="15" t="s">
         <v>180</v>
@@ -12372,7 +12563,7 @@
         <v>24</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H220" s="25">
         <v>42366</v>
@@ -12390,7 +12581,7 @@
         <v>181</v>
       </c>
       <c r="M220" s="18" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N220" s="7" t="s">
         <v>21</v>
@@ -12410,13 +12601,13 @@
         <v>132</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F221" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H221" s="25">
         <v>42372</v>
@@ -12431,9 +12622,11 @@
         <v>44445</v>
       </c>
       <c r="L221" s="7" t="s">
-        <v>719</v>
-      </c>
-      <c r="M221" s="18"/>
+        <v>714</v>
+      </c>
+      <c r="M221" s="36" t="s">
+        <v>757</v>
+      </c>
       <c r="N221" s="7" t="s">
         <v>21</v>
       </c>
@@ -12449,16 +12642,16 @@
         <v>647</v>
       </c>
       <c r="D222" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="E222" s="15" t="s">
         <v>460</v>
-      </c>
-      <c r="E222" s="15" t="s">
-        <v>461</v>
       </c>
       <c r="F222" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H222" s="25">
         <v>42992</v>
@@ -12473,10 +12666,10 @@
         <v>44823</v>
       </c>
       <c r="L222" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="M222" s="35" t="s">
-        <v>744</v>
+        <v>738</v>
+      </c>
+      <c r="M222" s="34" t="s">
+        <v>739</v>
       </c>
       <c r="N222" s="7" t="s">
         <v>21</v>
@@ -12493,7 +12686,7 @@
         <v>585</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E223" s="15" t="s">
         <v>68</v>
@@ -12502,7 +12695,7 @@
         <v>24</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H223" s="25">
         <v>42096</v>
@@ -12520,7 +12713,7 @@
         <v>69</v>
       </c>
       <c r="M223" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N223" s="7" t="s">
         <v>57</v>
@@ -12540,13 +12733,13 @@
         <v>386</v>
       </c>
       <c r="E224" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F224" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H224" s="25">
         <v>42397</v>
@@ -12561,9 +12754,11 @@
         <v>44783</v>
       </c>
       <c r="L224" s="7" t="s">
-        <v>720</v>
-      </c>
-      <c r="M224" s="18"/>
+        <v>715</v>
+      </c>
+      <c r="M224" s="38" t="s">
+        <v>794</v>
+      </c>
       <c r="N224" s="7" t="s">
         <v>21</v>
       </c>
@@ -12582,13 +12777,13 @@
         <v>71</v>
       </c>
       <c r="E225" s="15" t="s">
-        <v>464</v>
+        <v>365</v>
       </c>
       <c r="F225" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H225" s="25">
         <v>42067</v>
@@ -12605,7 +12800,9 @@
       <c r="L225" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="M225" s="18"/>
+      <c r="M225" s="36" t="s">
+        <v>785</v>
+      </c>
       <c r="N225" s="7" t="s">
         <v>57</v>
       </c>
@@ -12621,16 +12818,16 @@
         <v>691</v>
       </c>
       <c r="D226" s="14" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E226" s="15" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F226" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H226" s="25">
         <v>41854</v>
@@ -12645,7 +12842,7 @@
         <v>45148</v>
       </c>
       <c r="L226" s="7" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="M226" s="18"/>
       <c r="N226" s="7" t="s">
@@ -12663,16 +12860,16 @@
         <v>528</v>
       </c>
       <c r="D227" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E227" s="15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F227" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H227" s="25">
         <v>42018</v>
@@ -12687,9 +12884,11 @@
         <v>44236</v>
       </c>
       <c r="L227" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="M227" s="18"/>
+        <v>716</v>
+      </c>
+      <c r="M227" s="36" t="s">
+        <v>761</v>
+      </c>
       <c r="N227" s="7" t="s">
         <v>21</v>
       </c>
@@ -12705,7 +12904,7 @@
         <v>689</v>
       </c>
       <c r="D228" s="14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E228" s="15" t="s">
         <v>207</v>
@@ -12714,7 +12913,7 @@
         <v>24</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H228" s="25">
         <v>42083</v>
@@ -12729,7 +12928,7 @@
         <v>45207</v>
       </c>
       <c r="L228" s="7" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="M228" s="18"/>
       <c r="N228" s="7" t="s">
@@ -12747,7 +12946,7 @@
         <v>479</v>
       </c>
       <c r="D229" s="14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E229" s="15" t="s">
         <v>271</v>
@@ -12756,7 +12955,7 @@
         <v>24</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H229" s="25">
         <v>42037</v>
@@ -12771,9 +12970,11 @@
         <v>44124</v>
       </c>
       <c r="L229" s="7" t="s">
-        <v>722</v>
-      </c>
-      <c r="M229" s="18"/>
+        <v>717</v>
+      </c>
+      <c r="M229" s="36" t="s">
+        <v>771</v>
+      </c>
       <c r="N229" s="7" t="s">
         <v>21</v>
       </c>
@@ -12789,7 +12990,7 @@
         <v>648</v>
       </c>
       <c r="D230" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E230" s="15" t="s">
         <v>81</v>
@@ -12798,7 +12999,7 @@
         <v>24</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H230" s="25">
         <v>43023</v>
@@ -12813,10 +13014,10 @@
         <v>44852</v>
       </c>
       <c r="L230" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M230" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="N230" s="7" t="s">
         <v>21</v>
@@ -12833,7 +13034,7 @@
         <v>578</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E231" s="13" t="s">
         <v>340</v>
@@ -12842,7 +13043,7 @@
         <v>24</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H231" s="25">
         <v>41870</v>
@@ -12860,7 +13061,7 @@
         <v>341</v>
       </c>
       <c r="M231" s="29" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="N231" s="7" t="s">
         <v>57</v>
@@ -12884,18 +13085,26 @@
         <v>24</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H232" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H232" s="25">
+        <v>42729</v>
+      </c>
       <c r="I232" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J232" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K232" s="25"/>
-      <c r="L232" s="7"/>
-      <c r="M232" s="18"/>
+      <c r="K232" s="25">
+        <v>44778</v>
+      </c>
+      <c r="L232" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M232" s="36" t="s">
+        <v>568</v>
+      </c>
       <c r="N232" s="7" t="s">
         <v>21</v>
       </c>
@@ -12911,16 +13120,16 @@
         <v>587</v>
       </c>
       <c r="D233" s="14" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E233" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F233" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H233" s="25">
         <v>41704</v>
@@ -12935,7 +13144,7 @@
         <v>44783</v>
       </c>
       <c r="L233" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="M233" s="18"/>
       <c r="N233" s="7" t="s">
@@ -12953,16 +13162,16 @@
         <v>575</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E234" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F234" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H234" s="25">
         <v>42680</v>
@@ -12973,11 +13182,15 @@
       <c r="J234" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K234" s="25"/>
+      <c r="K234" s="25">
+        <v>45223</v>
+      </c>
       <c r="L234" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="M234" s="18"/>
+        <v>732</v>
+      </c>
+      <c r="M234" s="36" t="s">
+        <v>783</v>
+      </c>
       <c r="N234" s="7" t="s">
         <v>21</v>
       </c>
@@ -12993,16 +13206,16 @@
         <v>586</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E235" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F235" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H235" s="25">
         <v>42304</v>
@@ -13017,9 +13230,11 @@
         <v>44842</v>
       </c>
       <c r="L235" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="M235" s="18"/>
+        <v>718</v>
+      </c>
+      <c r="M235" s="36" t="s">
+        <v>758</v>
+      </c>
       <c r="N235" s="7" t="s">
         <v>21</v>
       </c>
@@ -13035,16 +13250,16 @@
         <v>583</v>
       </c>
       <c r="D236" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E236" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F236" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H236" s="25">
         <v>42308</v>
@@ -13059,9 +13274,11 @@
         <v>44783</v>
       </c>
       <c r="L236" s="7" t="s">
-        <v>724</v>
-      </c>
-      <c r="M236" s="18"/>
+        <v>719</v>
+      </c>
+      <c r="M236" s="36" t="s">
+        <v>770</v>
+      </c>
       <c r="N236" s="7" t="s">
         <v>21</v>
       </c>
@@ -13077,16 +13294,16 @@
         <v>580</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E237" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F237" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H237" s="25">
         <v>41840</v>
@@ -13101,10 +13318,10 @@
         <v>44842</v>
       </c>
       <c r="L237" s="7" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="M237" s="18" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="N237" s="7" t="s">
         <v>57</v>
@@ -13121,7 +13338,7 @@
         <v>480</v>
       </c>
       <c r="D238" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E238" s="15" t="s">
         <v>360</v>
@@ -13130,7 +13347,7 @@
         <v>24</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H238" s="25">
         <v>42053</v>
@@ -13145,9 +13362,11 @@
         <v>44124</v>
       </c>
       <c r="L238" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="M238" s="18"/>
+        <v>720</v>
+      </c>
+      <c r="M238" s="36" t="s">
+        <v>691</v>
+      </c>
       <c r="N238" s="7" t="s">
         <v>21</v>
       </c>
@@ -13172,7 +13391,7 @@
         <v>24</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H239" s="25">
         <v>42880</v>
@@ -13187,9 +13406,11 @@
         <v>44779</v>
       </c>
       <c r="L239" s="7" t="s">
-        <v>726</v>
-      </c>
-      <c r="M239" s="18"/>
+        <v>721</v>
+      </c>
+      <c r="M239" s="36" t="s">
+        <v>786</v>
+      </c>
       <c r="N239" s="7" t="s">
         <v>21</v>
       </c>
@@ -13205,16 +13426,16 @@
         <v>685</v>
       </c>
       <c r="D240" s="14" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E240" s="15" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F240" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H240" s="25">
         <v>41938</v>
@@ -13229,9 +13450,11 @@
         <v>45207</v>
       </c>
       <c r="L240" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="M240" s="18"/>
+        <v>751</v>
+      </c>
+      <c r="M240" s="36" t="s">
+        <v>769</v>
+      </c>
       <c r="N240" s="7" t="s">
         <v>21</v>
       </c>
@@ -13247,16 +13470,16 @@
         <v>688</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E241" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F241" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H241" s="25">
         <v>42029</v>
@@ -13271,9 +13494,11 @@
         <v>45207</v>
       </c>
       <c r="L241" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="M241" s="18"/>
+        <v>744</v>
+      </c>
+      <c r="M241" s="36" t="s">
+        <v>735</v>
+      </c>
       <c r="N241" s="7" t="s">
         <v>21</v>
       </c>
@@ -13289,7 +13514,7 @@
         <v>546</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="E242" s="15" t="s">
         <v>164</v>
@@ -13298,7 +13523,7 @@
         <v>24</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H242" s="25">
         <v>41857</v>
@@ -13313,9 +13538,11 @@
         <v>44445</v>
       </c>
       <c r="L242" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="M242" s="18"/>
+        <v>723</v>
+      </c>
+      <c r="M242" s="38" t="s">
+        <v>787</v>
+      </c>
       <c r="N242" s="7" t="s">
         <v>21</v>
       </c>
@@ -13329,16 +13556,16 @@
       </c>
       <c r="C243" s="20"/>
       <c r="D243" s="14" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E243" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F243" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H243" s="25">
         <v>42489</v>
@@ -13351,9 +13578,11 @@
       </c>
       <c r="K243" s="25"/>
       <c r="L243" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="M243" s="18"/>
+        <v>752</v>
+      </c>
+      <c r="M243" s="36" t="s">
+        <v>773</v>
+      </c>
       <c r="N243" s="7" t="s">
         <v>21</v>
       </c>
@@ -13367,16 +13596,16 @@
       </c>
       <c r="C244" s="20"/>
       <c r="D244" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E244" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F244" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H244" s="25">
         <v>42885</v>
@@ -13389,9 +13618,11 @@
       </c>
       <c r="K244" s="25"/>
       <c r="L244" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="M244" s="18"/>
+        <v>752</v>
+      </c>
+      <c r="M244" s="36" t="s">
+        <v>773</v>
+      </c>
       <c r="N244" s="7" t="s">
         <v>21</v>
       </c>
@@ -13405,16 +13636,16 @@
       </c>
       <c r="C245" s="20"/>
       <c r="D245" s="14" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F245" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H245" s="25"/>
       <c r="I245" s="20" t="s">
@@ -13441,16 +13672,16 @@
         <v>544</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F246" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H246" s="25">
         <v>42303</v>
@@ -13468,7 +13699,7 @@
         <v>69</v>
       </c>
       <c r="M246" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="N246" s="7" t="s">
         <v>57</v>
@@ -13485,16 +13716,16 @@
         <v>780</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F247" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H247" s="25">
         <v>42919</v>
@@ -13509,9 +13740,11 @@
         <v>45252</v>
       </c>
       <c r="L247" s="7" t="s">
-        <v>758</v>
-      </c>
-      <c r="M247" s="18"/>
+        <v>753</v>
+      </c>
+      <c r="M247" s="36" t="s">
+        <v>739</v>
+      </c>
       <c r="N247" s="7" t="s">
         <v>21</v>
       </c>
@@ -13527,16 +13760,16 @@
         <v>569</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F248" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H248" s="25">
         <v>42948</v>
@@ -13551,9 +13784,11 @@
         <v>44777</v>
       </c>
       <c r="L248" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="M248" s="18"/>
+        <v>724</v>
+      </c>
+      <c r="M248" s="38" t="s">
+        <v>788</v>
+      </c>
       <c r="N248" s="7" t="s">
         <v>21</v>
       </c>
@@ -13572,13 +13807,13 @@
         <v>109</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F249" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H249" s="25">
         <v>42135</v>
@@ -13593,9 +13828,11 @@
         <v>44783</v>
       </c>
       <c r="L249" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="M249" s="18"/>
+        <v>725</v>
+      </c>
+      <c r="M249" s="36" t="s">
+        <v>760</v>
+      </c>
       <c r="N249" s="7" t="s">
         <v>21</v>
       </c>
@@ -13611,16 +13848,16 @@
         <v>574</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E250" s="15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F250" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H250" s="25">
         <v>42554</v>
@@ -13635,9 +13872,11 @@
         <v>44778</v>
       </c>
       <c r="L250" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="M250" s="18"/>
+        <v>726</v>
+      </c>
+      <c r="M250" s="38" t="s">
+        <v>789</v>
+      </c>
       <c r="N250" s="7" t="s">
         <v>21</v>
       </c>
@@ -13653,16 +13892,16 @@
         <v>571</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F251" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H251" s="25">
         <v>41520</v>
@@ -13677,9 +13916,11 @@
         <v>44778</v>
       </c>
       <c r="L251" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="M251" s="18"/>
+        <v>727</v>
+      </c>
+      <c r="M251" s="36" t="s">
+        <v>759</v>
+      </c>
       <c r="N251" s="7" t="s">
         <v>21</v>
       </c>
@@ -13695,7 +13936,7 @@
         <v>526</v>
       </c>
       <c r="D252" s="14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E252" s="15" t="s">
         <v>293</v>
@@ -13704,7 +13945,7 @@
         <v>17</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H252" s="25">
         <v>42351</v>
@@ -13722,7 +13963,7 @@
         <v>294</v>
       </c>
       <c r="M252" s="29" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="N252" s="7" t="s">
         <v>57</v>
@@ -13739,16 +13980,16 @@
         <v>537</v>
       </c>
       <c r="D253" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F253" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H253" s="25">
         <v>42574</v>
@@ -13763,9 +14004,11 @@
         <v>44443</v>
       </c>
       <c r="L253" s="7" t="s">
-        <v>733</v>
-      </c>
-      <c r="M253" s="18"/>
+        <v>728</v>
+      </c>
+      <c r="M253" s="38" t="s">
+        <v>790</v>
+      </c>
       <c r="N253" s="7" t="s">
         <v>21</v>
       </c>
@@ -13784,13 +14027,13 @@
         <v>398</v>
       </c>
       <c r="E254" s="15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F254" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H254" s="25">
         <v>42434</v>
@@ -13805,10 +14048,10 @@
         <v>44783</v>
       </c>
       <c r="L254" s="7" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="M254" s="18" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="N254" s="7" t="s">
         <v>57</v>
@@ -13834,18 +14077,24 @@
         <v>17</v>
       </c>
       <c r="G255" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H255" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H255" s="25">
+        <v>42376</v>
+      </c>
       <c r="I255" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J255" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K255" s="25"/>
+      <c r="K255" s="25">
+        <v>44440</v>
+      </c>
       <c r="L255" s="7"/>
-      <c r="M255" s="18"/>
+      <c r="M255" s="38" t="s">
+        <v>791</v>
+      </c>
       <c r="N255" s="7" t="s">
         <v>21</v>
       </c>
@@ -13859,7 +14108,7 @@
       </c>
       <c r="C256" s="20"/>
       <c r="D256" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E256" s="15" t="s">
         <v>100</v>
@@ -13868,21 +14117,25 @@
         <v>17</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H256" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H256" s="25">
+        <v>41998</v>
+      </c>
       <c r="I256" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J256" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K256" s="25"/>
+      <c r="K256" s="25">
+        <v>45148</v>
+      </c>
       <c r="L256" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M256" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="N256" s="7" t="s">
         <v>21</v>
@@ -13897,7 +14150,7 @@
       </c>
       <c r="C257" s="20"/>
       <c r="D257" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E257" s="15" t="s">
         <v>264</v>
@@ -13906,21 +14159,25 @@
         <v>17</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H257" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H257" s="25">
+        <v>42736</v>
+      </c>
       <c r="I257" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J257" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K257" s="25"/>
+      <c r="K257" s="25">
+        <v>44842</v>
+      </c>
       <c r="L257" s="7" t="s">
         <v>265</v>
       </c>
       <c r="M257" s="18" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="N257" s="7" t="s">
         <v>21</v>
@@ -13935,27 +14192,35 @@
       </c>
       <c r="C258" s="20"/>
       <c r="D258" s="14" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E258" s="15" t="s">
-        <v>509</v>
+        <v>343</v>
       </c>
       <c r="F258" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H258" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H258" s="25">
+        <v>41623</v>
+      </c>
       <c r="I258" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J258" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K258" s="25"/>
-      <c r="L258" s="7"/>
-      <c r="M258" s="18"/>
+      <c r="K258" s="25">
+        <v>44774</v>
+      </c>
+      <c r="L258" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="M258" s="36" t="s">
+        <v>764</v>
+      </c>
       <c r="N258" s="7" t="s">
         <v>21</v>
       </c>
@@ -13969,7 +14234,7 @@
       </c>
       <c r="C259" s="20"/>
       <c r="D259" s="14" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E259" s="15" t="s">
         <v>165</v>
@@ -13978,7 +14243,7 @@
         <v>17</v>
       </c>
       <c r="G259" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H259" s="25">
         <v>42128</v>
@@ -13989,9 +14254,11 @@
       <c r="J259" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K259" s="25"/>
+      <c r="K259" s="25">
+        <v>45148</v>
+      </c>
       <c r="L259" s="7" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="M259" s="18"/>
       <c r="N259" s="7" t="s">
@@ -14007,18 +14274,20 @@
       </c>
       <c r="C260" s="20"/>
       <c r="D260" s="14" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E260" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F260" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H260" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H260" s="25">
+        <v>42199</v>
+      </c>
       <c r="I260" s="20" t="s">
         <v>19</v>
       </c>
@@ -14026,8 +14295,12 @@
         <v>20</v>
       </c>
       <c r="K260" s="25"/>
-      <c r="L260" s="7"/>
-      <c r="M260" s="18"/>
+      <c r="L260" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="M260" s="36" t="s">
+        <v>766</v>
+      </c>
       <c r="N260" s="7" t="s">
         <v>21</v>
       </c>
@@ -14041,18 +14314,20 @@
       </c>
       <c r="C261" s="20"/>
       <c r="D261" s="14" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F261" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H261" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H261" s="25">
+        <v>41075</v>
+      </c>
       <c r="I261" s="20" t="s">
         <v>19</v>
       </c>
@@ -14060,12 +14335,16 @@
         <v>20</v>
       </c>
       <c r="K261" s="25"/>
-      <c r="L261" s="7"/>
-      <c r="M261" s="18"/>
+      <c r="L261" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="M261" s="36" t="s">
+        <v>768</v>
+      </c>
       <c r="N261" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P261" s="36"/>
+      <c r="P261" s="35"/>
     </row>
     <row r="262" spans="1:16" ht="15.75">
       <c r="A262" s="18">
@@ -14076,29 +14355,35 @@
       </c>
       <c r="C262" s="20"/>
       <c r="D262" s="14" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E262" s="15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F262" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H262" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H262" s="25">
+        <v>42219</v>
+      </c>
       <c r="I262" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J262" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K262" s="25"/>
+      <c r="K262" s="25">
+        <v>45139</v>
+      </c>
       <c r="L262" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="M262" s="18"/>
+        <v>667</v>
+      </c>
+      <c r="M262" s="36" t="s">
+        <v>668</v>
+      </c>
       <c r="N262" s="7" t="s">
         <v>21</v>
       </c>
@@ -14112,18 +14397,20 @@
       </c>
       <c r="C263" s="20"/>
       <c r="D263" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F263" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H263" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H263" s="25">
+        <v>42413</v>
+      </c>
       <c r="I263" s="20" t="s">
         <v>19</v>
       </c>
@@ -14132,9 +14419,11 @@
       </c>
       <c r="K263" s="25"/>
       <c r="L263" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="M263" s="18"/>
+        <v>755</v>
+      </c>
+      <c r="M263" s="36" t="s">
+        <v>772</v>
+      </c>
       <c r="N263" s="7" t="s">
         <v>21</v>
       </c>
@@ -14157,7 +14446,7 @@
         <v>17</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H264" s="25">
         <v>42938</v>
@@ -14175,7 +14464,7 @@
         <v>121</v>
       </c>
       <c r="M264" s="18" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N264" s="18" t="s">
         <v>57</v>
@@ -14199,7 +14488,7 @@
         <v>17</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H265" s="25">
         <v>43436</v>
@@ -14217,7 +14506,7 @@
         <v>121</v>
       </c>
       <c r="M265" s="18" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N265" s="18" t="s">
         <v>57</v>
@@ -14232,7 +14521,7 @@
       </c>
       <c r="C266" s="20"/>
       <c r="D266" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E266" s="15" t="s">
         <v>103</v>
@@ -14241,20 +14530,26 @@
         <v>17</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H266" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H266" s="25">
+        <v>42018</v>
+      </c>
       <c r="I266" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J266" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="K266" s="25"/>
+      <c r="K266" s="5">
+        <v>45505</v>
+      </c>
       <c r="L266" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="M266" s="18"/>
+        <v>104</v>
+      </c>
+      <c r="M266" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="N266" s="7" t="s">
         <v>21</v>
       </c>
@@ -14268,16 +14563,16 @@
       </c>
       <c r="C267" s="20"/>
       <c r="D267" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F267" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G267" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H267" s="25"/>
       <c r="I267" s="20" t="s">
@@ -14288,7 +14583,7 @@
       </c>
       <c r="K267" s="25"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="18"/>
+      <c r="M267" s="38"/>
       <c r="N267" s="7" t="s">
         <v>21</v>
       </c>
@@ -14302,18 +14597,20 @@
       </c>
       <c r="C268" s="20"/>
       <c r="D268" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E268" s="15" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F268" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G268" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="H268" s="25"/>
+        <v>453</v>
+      </c>
+      <c r="H268" s="25">
+        <v>42087</v>
+      </c>
       <c r="I268" s="20" t="s">
         <v>19</v>
       </c>
@@ -14321,8 +14618,12 @@
         <v>20</v>
       </c>
       <c r="K268" s="25"/>
-      <c r="L268" s="7"/>
-      <c r="M268" s="18"/>
+      <c r="L268" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="M268" s="36" t="s">
+        <v>763</v>
+      </c>
       <c r="N268" s="7" t="s">
         <v>21</v>
       </c>
@@ -14336,16 +14637,16 @@
       </c>
       <c r="C269" s="20"/>
       <c r="D269" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E269" s="15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F269" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G269" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H269" s="25"/>
       <c r="I269" s="20" t="s">
@@ -14370,16 +14671,16 @@
       </c>
       <c r="C270" s="20"/>
       <c r="D270" s="14" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E270" s="15" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F270" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G270" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H270" s="25"/>
       <c r="I270" s="20" t="s">
@@ -14420,14 +14721,14 @@
   <conditionalFormatting sqref="C217:C245">
     <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C246:C270">
+    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C246:C270">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -14447,7 +14748,7 @@
     <row r="1" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1"/>
     <row r="2" spans="1:2" s="2" customFormat="1" ht="21">
       <c r="A2" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Female")</f>
@@ -14456,7 +14757,7 @@
     </row>
     <row r="3" spans="1:2" ht="21">
       <c r="A3" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF('All Record'!$F$2:$F$1048576,"Male")</f>
@@ -14465,7 +14766,7 @@
     </row>
     <row r="4" spans="1:2" ht="21">
       <c r="A4" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B4" s="4">
         <f>B2+B3</f>

--- a/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE661728-CB9A-4B8A-9B99-E436029A7CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFF8DBA-B32B-49C4-A786-834A712F3FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Record" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="793">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -1916,9 +1916,6 @@
   </si>
   <si>
     <t>0333-2431468</t>
-  </si>
-  <si>
-    <t>0332-269970</t>
   </si>
   <si>
     <t>0307-2469614</t>
@@ -2683,7 +2680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2744,9 +2741,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2759,6 +2753,11 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3368,22 +3367,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:14" s="11" customFormat="1" ht="15.75">
       <c r="A2" s="8" t="s">
@@ -5054,8 +5053,8 @@
       <c r="L41" s="39" t="s">
         <v>416</v>
       </c>
-      <c r="M41" s="43" t="s">
-        <v>780</v>
+      <c r="M41" s="42" t="s">
+        <v>779</v>
       </c>
       <c r="N41" s="39" t="s">
         <v>57</v>
@@ -5291,7 +5290,7 @@
       <c r="G47" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H47" s="44"/>
+      <c r="H47" s="43"/>
       <c r="I47" s="38" t="s">
         <v>19</v>
       </c>
@@ -5318,11 +5317,11 @@
       <c r="B48" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="46" t="s">
+      <c r="C48" s="44"/>
+      <c r="D48" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="47" t="s">
+      <c r="E48" s="46" t="s">
         <v>126</v>
       </c>
       <c r="F48" s="33" t="s">
@@ -5365,7 +5364,7 @@
         <v>128</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F49" s="33" t="s">
         <v>24</v>
@@ -5373,7 +5372,7 @@
       <c r="G49" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="44"/>
+      <c r="H49" s="43"/>
       <c r="I49" s="38" t="s">
         <v>19</v>
       </c>
@@ -5480,11 +5479,11 @@
       <c r="B52" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="48"/>
+      <c r="C52" s="47"/>
       <c r="D52" s="33" t="s">
         <v>593</v>
       </c>
-      <c r="E52" s="49" t="s">
+      <c r="E52" s="48" t="s">
         <v>594</v>
       </c>
       <c r="F52" s="33" t="s">
@@ -5515,7 +5514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:14" s="52" customFormat="1" ht="15.75">
+    <row r="53" spans="1:14" s="51" customFormat="1" ht="15.75">
       <c r="A53" s="33">
         <v>1</v>
       </c>
@@ -5526,7 +5525,7 @@
       <c r="D53" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="50" t="s">
+      <c r="E53" s="49" t="s">
         <v>135</v>
       </c>
       <c r="F53" s="33" t="s">
@@ -5535,7 +5534,7 @@
       <c r="G53" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H53" s="51">
+      <c r="H53" s="50">
         <v>44251</v>
       </c>
       <c r="I53" s="38" t="s">
@@ -5544,7 +5543,7 @@
       <c r="J53" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="K53" s="51">
+      <c r="K53" s="50">
         <v>45303</v>
       </c>
       <c r="L53" s="39" t="s">
@@ -5555,7 +5554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:14" s="52" customFormat="1" ht="15.75">
+    <row r="54" spans="1:14" s="51" customFormat="1" ht="15.75">
       <c r="A54" s="33">
         <v>2</v>
       </c>
@@ -5575,7 +5574,7 @@
       <c r="G54" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H54" s="51">
+      <c r="H54" s="50">
         <v>43239</v>
       </c>
       <c r="I54" s="38" t="s">
@@ -5584,7 +5583,7 @@
       <c r="J54" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="K54" s="51">
+      <c r="K54" s="50">
         <v>45139</v>
       </c>
       <c r="L54" s="39" t="s">
@@ -5597,7 +5596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:14" s="52" customFormat="1" ht="15.75">
+    <row r="55" spans="1:14" s="51" customFormat="1" ht="15.75">
       <c r="A55" s="33">
         <v>3</v>
       </c>
@@ -5617,7 +5616,7 @@
       <c r="G55" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H55" s="51">
+      <c r="H55" s="50">
         <v>43326</v>
       </c>
       <c r="I55" s="38" t="s">
@@ -5626,7 +5625,7 @@
       <c r="J55" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="K55" s="51"/>
+      <c r="K55" s="43"/>
       <c r="L55" s="39" t="s">
         <v>143</v>
       </c>
@@ -5637,1803 +5636,1803 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15.75">
-      <c r="A56" s="16">
+    <row r="56" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A56" s="33">
         <v>4</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="18"/>
-      <c r="D56" s="14" t="s">
+      <c r="B56" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="38"/>
+      <c r="D56" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="F56" s="16" t="s">
+      <c r="F56" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H56" s="20">
+      <c r="H56" s="50">
         <v>43110</v>
       </c>
-      <c r="I56" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="20">
+      <c r="I56" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="50">
         <v>45139</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="L56" s="39" t="s">
         <v>599</v>
       </c>
-      <c r="M56" s="28" t="s">
-        <v>728</v>
-      </c>
-      <c r="N56" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="15.75">
-      <c r="A57" s="16">
+      <c r="M56" s="53" t="s">
+        <v>727</v>
+      </c>
+      <c r="N56" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A57" s="33">
         <v>5</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="18"/>
-      <c r="D57" s="14" t="s">
+      <c r="B57" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="38"/>
+      <c r="D57" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="F57" s="16" t="s">
+      <c r="F57" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H57" s="20">
+      <c r="H57" s="50">
         <v>43367</v>
       </c>
-      <c r="I57" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J57" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="20">
+      <c r="I57" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="50">
         <v>45139</v>
       </c>
-      <c r="L57" s="7" t="s">
+      <c r="L57" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="M57" s="16" t="s">
+      <c r="M57" s="33" t="s">
         <v>600</v>
       </c>
-      <c r="N57" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="15.75">
-      <c r="A58" s="16">
+      <c r="N57" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A58" s="33">
         <v>6</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="18"/>
-      <c r="D58" s="14" t="s">
+      <c r="B58" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="38"/>
+      <c r="D58" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="F58" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="G58" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H58" s="20">
+      <c r="H58" s="50">
         <v>43559</v>
       </c>
-      <c r="I58" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="20">
+      <c r="I58" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="50">
         <v>45143</v>
       </c>
-      <c r="L58" s="7" t="s">
+      <c r="L58" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="M58" s="16" t="s">
+      <c r="M58" s="33" t="s">
         <v>601</v>
       </c>
-      <c r="N58" s="16" t="s">
+      <c r="N58" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15.75">
-      <c r="A59" s="16">
+    <row r="59" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A59" s="33">
         <v>7</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="18"/>
-      <c r="D59" s="14" t="s">
+      <c r="B59" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="38"/>
+      <c r="D59" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="E59" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="F59" s="16" t="s">
+      <c r="E59" s="36" t="s">
+        <v>695</v>
+      </c>
+      <c r="F59" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G59" s="16" t="s">
+      <c r="G59" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H59" s="20">
+      <c r="H59" s="50">
         <v>43593</v>
       </c>
-      <c r="I59" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="20">
+      <c r="I59" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="50">
         <v>45143</v>
       </c>
-      <c r="L59" s="7" t="s">
+      <c r="L59" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="M59" s="16" t="s">
+      <c r="M59" s="33" t="s">
         <v>602</v>
       </c>
-      <c r="N59" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="15.75">
-      <c r="A60" s="16">
+      <c r="N59" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A60" s="33">
         <v>8</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="18"/>
-      <c r="D60" s="14" t="s">
+      <c r="B60" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="38"/>
+      <c r="D60" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="F60" s="16" t="s">
+      <c r="F60" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G60" s="16" t="s">
+      <c r="G60" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H60" s="20">
+      <c r="H60" s="50">
         <v>44174</v>
       </c>
-      <c r="I60" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="20">
+      <c r="I60" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="50">
         <v>45173</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="L60" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="M60" s="16" t="s">
+      <c r="M60" s="33" t="s">
         <v>603</v>
       </c>
-      <c r="N60" s="16" t="s">
+      <c r="N60" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15.75">
-      <c r="A61" s="16">
+    <row r="61" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A61" s="33">
         <v>9</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="18"/>
-      <c r="D61" s="14" t="s">
+      <c r="B61" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="38"/>
+      <c r="D61" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="F61" s="16" t="s">
+      <c r="F61" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H61" s="20">
+      <c r="H61" s="43">
         <v>44703</v>
       </c>
-      <c r="I61" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="20">
+      <c r="I61" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="50">
         <v>45231</v>
       </c>
-      <c r="L61" s="7" t="s">
+      <c r="L61" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="M61" s="16" t="s">
+      <c r="M61" s="33" t="s">
         <v>604</v>
       </c>
-      <c r="N61" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="15.75">
-      <c r="A62" s="16">
+      <c r="N61" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A62" s="33">
         <v>10</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="14" t="s">
+      <c r="B62" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="F62" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="G62" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H62" s="20">
+      <c r="H62" s="50">
         <v>43714</v>
       </c>
-      <c r="I62" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="20">
+      <c r="I62" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="50">
         <v>45145</v>
       </c>
-      <c r="L62" s="7" t="s">
+      <c r="L62" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="M62" s="16" t="s">
+      <c r="M62" s="33" t="s">
         <v>605</v>
       </c>
-      <c r="N62" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="15.75">
-      <c r="A63" s="16">
+      <c r="N62" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A63" s="33">
         <v>11</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63" s="18"/>
-      <c r="D63" s="14" t="s">
+      <c r="B63" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="38"/>
+      <c r="D63" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="G63" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H63" s="20">
+      <c r="H63" s="50">
         <v>44029</v>
       </c>
-      <c r="I63" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="20">
+      <c r="I63" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="50">
         <v>45143</v>
       </c>
-      <c r="L63" s="7" t="s">
+      <c r="L63" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="M63" s="16" t="s">
+      <c r="M63" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="N63" s="16" t="s">
+      <c r="N63" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15.75">
-      <c r="A64" s="16">
+    <row r="64" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A64" s="33">
         <v>12</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="18"/>
-      <c r="D64" s="14" t="s">
+      <c r="B64" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="38"/>
+      <c r="D64" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="F64" s="16" t="s">
+      <c r="F64" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="G64" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H64" s="20">
+      <c r="H64" s="50">
         <v>43593</v>
       </c>
-      <c r="I64" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="20">
+      <c r="I64" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="50">
         <v>45140</v>
       </c>
-      <c r="L64" s="7" t="s">
+      <c r="L64" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="M64" s="16" t="s">
+      <c r="M64" s="33" t="s">
         <v>607</v>
       </c>
-      <c r="N64" s="16" t="s">
+      <c r="N64" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15.75">
-      <c r="A65" s="16">
+    <row r="65" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A65" s="33">
         <v>13</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="18"/>
-      <c r="D65" s="14" t="s">
+      <c r="B65" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="38"/>
+      <c r="D65" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="F65" s="16" t="s">
+      <c r="F65" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="G65" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H65" s="20">
+      <c r="H65" s="50">
         <v>42982</v>
       </c>
-      <c r="I65" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="20">
+      <c r="I65" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="50">
         <v>45139</v>
       </c>
-      <c r="L65" s="7" t="s">
+      <c r="L65" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="M65" s="16" t="s">
+      <c r="M65" s="33" t="s">
         <v>608</v>
       </c>
-      <c r="N65" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="15.75">
-      <c r="A66" s="16">
+      <c r="N65" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A66" s="33">
         <v>14</v>
       </c>
-      <c r="B66" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="18"/>
-      <c r="D66" s="14" t="s">
+      <c r="B66" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="38"/>
+      <c r="D66" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="F66" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H66" s="20">
+      <c r="H66" s="50">
         <v>43727</v>
       </c>
-      <c r="I66" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="20">
+      <c r="I66" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="50">
         <v>45139</v>
       </c>
-      <c r="L66" s="7" t="s">
+      <c r="L66" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="M66" s="16" t="s">
+      <c r="M66" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="N66" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.75">
-      <c r="A67" s="16">
-        <v>15</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C67" s="18"/>
-      <c r="D67" s="14" t="s">
+      <c r="N66" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A67" s="33">
+        <v>15</v>
+      </c>
+      <c r="B67" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="38"/>
+      <c r="D67" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F67" s="16" t="s">
+      <c r="F67" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="G67" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H67" s="20">
+      <c r="H67" s="50">
         <v>43749</v>
       </c>
-      <c r="I67" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K67" s="20">
+      <c r="I67" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="50">
         <v>45139</v>
       </c>
-      <c r="L67" s="7" t="s">
+      <c r="L67" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="M67" s="16" t="s">
+      <c r="M67" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="N67" s="7" t="s">
+      <c r="N67" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="15.75">
-      <c r="A68" s="16">
+    <row r="68" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A68" s="33">
         <v>16</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="18"/>
-      <c r="D68" s="14" t="s">
+      <c r="B68" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="38"/>
+      <c r="D68" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="F68" s="16" t="s">
+      <c r="F68" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G68" s="16" t="s">
+      <c r="G68" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H68" s="20">
+      <c r="H68" s="50">
         <v>43232</v>
       </c>
-      <c r="I68" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="20">
+      <c r="I68" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="50">
         <v>45139</v>
       </c>
-      <c r="L68" s="7" t="s">
+      <c r="L68" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="M68" s="16" t="s">
+      <c r="M68" s="33" t="s">
         <v>609</v>
       </c>
-      <c r="N68" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="15.75">
-      <c r="A69" s="16">
+      <c r="N68" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A69" s="33">
         <v>17</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C69" s="18"/>
-      <c r="D69" s="14" t="s">
+      <c r="B69" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="38"/>
+      <c r="D69" s="41" t="s">
         <v>179</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E69" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="F69" s="16" t="s">
+      <c r="F69" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="G69" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H69" s="20">
+      <c r="H69" s="50">
         <v>43728</v>
       </c>
-      <c r="I69" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69" s="20">
+      <c r="I69" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="50">
         <v>45139</v>
       </c>
-      <c r="L69" s="7" t="s">
+      <c r="L69" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="M69" s="16" t="s">
+      <c r="M69" s="33" t="s">
         <v>610</v>
       </c>
-      <c r="N69" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="15.75">
-      <c r="A70" s="16">
+      <c r="N69" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A70" s="33">
         <v>18</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="18"/>
-      <c r="D70" s="14" t="s">
+      <c r="B70" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="38"/>
+      <c r="D70" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="F70" s="16" t="s">
+      <c r="F70" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G70" s="16" t="s">
+      <c r="G70" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="20">
+      <c r="H70" s="50">
         <v>43946</v>
       </c>
-      <c r="I70" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J70" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K70" s="20">
+      <c r="I70" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="50">
         <v>45143</v>
       </c>
-      <c r="L70" s="7" t="s">
+      <c r="L70" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="M70" s="16" t="s">
+      <c r="M70" s="33" t="s">
         <v>611</v>
       </c>
-      <c r="N70" s="16" t="s">
+      <c r="N70" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15.75">
-      <c r="A71" s="16">
-        <v>19</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="14" t="s">
+    <row r="71" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A71" s="33">
+        <v>19</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="38"/>
+      <c r="D71" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="F71" s="16" t="s">
+      <c r="F71" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H71" s="20">
+      <c r="H71" s="50">
         <v>43572</v>
       </c>
-      <c r="I71" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J71" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K71" s="20">
+      <c r="I71" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="50">
         <v>45143</v>
       </c>
-      <c r="L71" s="7" t="s">
+      <c r="L71" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="M71" s="16" t="s">
+      <c r="M71" s="33" t="s">
         <v>550</v>
       </c>
-      <c r="N71" s="7" t="s">
+      <c r="N71" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15.75">
-      <c r="A72" s="16">
-        <v>20</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="18"/>
-      <c r="D72" s="14" t="s">
+    <row r="72" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A72" s="33">
+        <v>20</v>
+      </c>
+      <c r="B72" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="38"/>
+      <c r="D72" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="F72" s="16" t="s">
+      <c r="F72" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G72" s="16" t="s">
+      <c r="G72" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H72" s="20">
+      <c r="H72" s="50">
         <v>43350</v>
       </c>
-      <c r="I72" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" s="20">
+      <c r="I72" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="50">
         <v>44775</v>
       </c>
-      <c r="L72" s="7" t="s">
+      <c r="L72" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="M72" s="16" t="s">
+      <c r="M72" s="33" t="s">
         <v>612</v>
       </c>
-      <c r="N72" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="15.75">
-      <c r="A73" s="16">
-        <v>21</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="14" t="s">
+      <c r="N72" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A73" s="33">
+        <v>21</v>
+      </c>
+      <c r="B73" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="38"/>
+      <c r="D73" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="F73" s="16" t="s">
+      <c r="F73" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G73" s="16" t="s">
+      <c r="G73" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H73" s="20">
+      <c r="H73" s="50">
         <v>43432</v>
       </c>
-      <c r="I73" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K73" s="20">
+      <c r="I73" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="50">
         <v>45143</v>
       </c>
-      <c r="L73" s="7" t="s">
+      <c r="L73" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="M73" s="16" t="s">
+      <c r="M73" s="33" t="s">
         <v>613</v>
       </c>
-      <c r="N73" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="15.75">
-      <c r="A74" s="16">
+      <c r="N73" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A74" s="33">
         <v>22</v>
       </c>
-      <c r="B74" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="14" t="s">
+      <c r="B74" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="38"/>
+      <c r="D74" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="F74" s="16" t="s">
+      <c r="F74" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="G74" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H74" s="20">
+      <c r="H74" s="50">
         <v>43789</v>
       </c>
-      <c r="I74" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K74" s="20">
+      <c r="I74" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="50">
         <v>45174</v>
       </c>
-      <c r="L74" s="7" t="s">
+      <c r="L74" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="M74" s="16" t="s">
+      <c r="M74" s="33" t="s">
         <v>614</v>
       </c>
-      <c r="N74" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="15.75">
-      <c r="A75" s="16">
+      <c r="N74" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A75" s="33">
         <v>23</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="14" t="s">
+      <c r="B75" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="38"/>
+      <c r="D75" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="F75" s="16" t="s">
+      <c r="F75" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G75" s="16" t="s">
+      <c r="G75" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H75" s="20">
+      <c r="H75" s="50">
         <v>43016</v>
       </c>
-      <c r="I75" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K75" s="20">
+      <c r="I75" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="50">
         <v>45180</v>
       </c>
-      <c r="L75" s="7" t="s">
+      <c r="L75" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="M75" s="16" t="s">
+      <c r="M75" s="33" t="s">
         <v>615</v>
       </c>
-      <c r="N75" s="7" t="s">
+      <c r="N75" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15.75">
-      <c r="A76" s="16">
+    <row r="76" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A76" s="33">
         <v>24</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="18"/>
-      <c r="D76" s="14" t="s">
+      <c r="B76" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="38"/>
+      <c r="D76" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="F76" s="16" t="s">
+      <c r="F76" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H76" s="20">
+      <c r="H76" s="50">
         <v>43490</v>
       </c>
-      <c r="I76" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K76" s="20">
+      <c r="I76" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="50">
         <v>45180</v>
       </c>
-      <c r="L76" s="7" t="s">
+      <c r="L76" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="M76" s="16" t="s">
+      <c r="M76" s="33" t="s">
         <v>616</v>
       </c>
-      <c r="N76" s="7" t="s">
+      <c r="N76" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75">
-      <c r="A77" s="16">
+    <row r="77" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A77" s="33">
         <v>25</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="14" t="s">
+      <c r="B77" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="38"/>
+      <c r="D77" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="E77" s="15" t="s">
+      <c r="E77" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="F77" s="16" t="s">
+      <c r="F77" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="G77" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H77" s="20">
+      <c r="H77" s="50">
         <v>43230</v>
       </c>
-      <c r="I77" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J77" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K77" s="20">
+      <c r="I77" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="50">
         <v>45180</v>
       </c>
-      <c r="L77" s="7" t="s">
+      <c r="L77" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="M77" s="16" t="s">
+      <c r="M77" s="33" t="s">
         <v>616</v>
       </c>
-      <c r="N77" s="7" t="s">
+      <c r="N77" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.75">
-      <c r="A78" s="16">
+    <row r="78" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A78" s="33">
         <v>26</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" s="18"/>
-      <c r="D78" s="14" t="s">
+      <c r="B78" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="38"/>
+      <c r="D78" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="E78" s="15" t="s">
+      <c r="E78" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="F78" s="16" t="s">
+      <c r="F78" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G78" s="16" t="s">
+      <c r="G78" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H78" s="20">
+      <c r="H78" s="50">
         <v>42721</v>
       </c>
-      <c r="I78" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J78" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78" s="20">
+      <c r="I78" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="50">
         <v>45519</v>
       </c>
-      <c r="L78" s="7" t="s">
+      <c r="L78" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="M78" s="16" t="s">
+      <c r="M78" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="N78" s="7" t="s">
+      <c r="N78" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15.75">
-      <c r="A79" s="16">
+    <row r="79" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A79" s="33">
         <v>27</v>
       </c>
-      <c r="B79" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="18"/>
-      <c r="D79" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="E79" s="15" t="s">
+      <c r="B79" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="38"/>
+      <c r="D79" s="41" t="s">
+        <v>635</v>
+      </c>
+      <c r="E79" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="F79" s="16" t="s">
+      <c r="F79" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G79" s="16" t="s">
+      <c r="G79" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H79" s="20">
+      <c r="H79" s="50">
         <v>43306</v>
       </c>
-      <c r="I79" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J79" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="20">
+      <c r="I79" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="50">
         <v>45519</v>
       </c>
-      <c r="L79" s="7" t="s">
+      <c r="L79" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="M79" s="16" t="s">
+      <c r="M79" s="33" t="s">
         <v>537</v>
       </c>
-      <c r="N79" s="7" t="s">
+      <c r="N79" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15.75">
-      <c r="A80" s="16">
+    <row r="80" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A80" s="33">
         <v>28</v>
       </c>
-      <c r="B80" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" s="18"/>
-      <c r="D80" s="14" t="s">
+      <c r="B80" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="38"/>
+      <c r="D80" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="E80" s="15" t="s">
+      <c r="E80" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="F80" s="16" t="s">
+      <c r="F80" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="16" t="s">
+      <c r="G80" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H80" s="20"/>
-      <c r="I80" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J80" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K80" s="20">
+      <c r="H80" s="43"/>
+      <c r="I80" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="50">
         <v>45519</v>
       </c>
-      <c r="L80" s="7" t="s">
+      <c r="L80" s="39" t="s">
         <v>563</v>
       </c>
-      <c r="M80" s="25" t="s">
+      <c r="M80" s="54" t="s">
+        <v>700</v>
+      </c>
+      <c r="N80" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A81" s="33">
+        <v>29</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="38"/>
+      <c r="D81" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>405</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="G81" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H81" s="50">
+        <v>44019</v>
+      </c>
+      <c r="I81" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="50">
+        <v>45537</v>
+      </c>
+      <c r="L81" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M81" s="54" t="s">
         <v>701</v>
       </c>
-      <c r="N80" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="15.75">
-      <c r="A81" s="16">
-        <v>29</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C81" s="18"/>
-      <c r="D81" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="E81" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="F81" s="16" t="s">
+      <c r="N81" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A82" s="33">
+        <v>30</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="38"/>
+      <c r="D82" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>617</v>
+      </c>
+      <c r="F82" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="G81" s="16" t="s">
+      <c r="G82" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="20">
-        <v>44019</v>
-      </c>
-      <c r="I81" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J81" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K81" s="20">
+      <c r="H82" s="50">
+        <v>43325</v>
+      </c>
+      <c r="I82" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="50">
+        <v>45519</v>
+      </c>
+      <c r="L82" s="39" t="s">
+        <v>618</v>
+      </c>
+      <c r="M82" s="33" t="s">
+        <v>619</v>
+      </c>
+      <c r="N82" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A83" s="33">
+        <v>32</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="38"/>
+      <c r="D83" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E83" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="F83" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="G83" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H83" s="50">
+        <v>43236</v>
+      </c>
+      <c r="I83" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="50">
         <v>45537</v>
       </c>
-      <c r="L81" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="M81" s="25" t="s">
+      <c r="L83" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="M83" s="33" t="s">
+        <v>622</v>
+      </c>
+      <c r="N83" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A84" s="33">
+        <v>33</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="34"/>
+      <c r="D84" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H84" s="50">
+        <v>43180</v>
+      </c>
+      <c r="I84" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="50">
+        <v>45166</v>
+      </c>
+      <c r="L84" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="M84" s="54" t="s">
         <v>702</v>
       </c>
-      <c r="N81" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="15.75">
-      <c r="A82" s="16">
-        <v>30</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="18"/>
-      <c r="D82" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>617</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G82" s="16" t="s">
+      <c r="N84" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A85" s="33">
+        <v>34</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="38"/>
+      <c r="D85" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E85" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H82" s="20">
-        <v>43325</v>
-      </c>
-      <c r="I82" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J82" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K82" s="20">
-        <v>45519</v>
-      </c>
-      <c r="L82" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="M82" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="N82" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="15.75">
-      <c r="A83" s="16">
-        <v>32</v>
-      </c>
-      <c r="B83" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" s="18"/>
-      <c r="D83" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G83" s="16" t="s">
+      <c r="H85" s="50">
+        <v>44000</v>
+      </c>
+      <c r="I85" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85" s="50">
+        <v>45139</v>
+      </c>
+      <c r="L85" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="M85" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="N85" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A86" s="33">
+        <v>35</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="38"/>
+      <c r="D86" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H83" s="20">
-        <v>43236</v>
-      </c>
-      <c r="I83" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J83" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83" s="20">
-        <v>45537</v>
-      </c>
-      <c r="L83" s="7" t="s">
-        <v>621</v>
-      </c>
-      <c r="M83" s="16" t="s">
-        <v>622</v>
-      </c>
-      <c r="N83" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="15.75">
-      <c r="A84" s="16">
-        <v>33</v>
-      </c>
-      <c r="B84" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="F84" s="16" t="s">
+      <c r="H86" s="50">
+        <v>44174</v>
+      </c>
+      <c r="I86" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="50">
+        <v>45173</v>
+      </c>
+      <c r="L86" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="M86" s="33" t="s">
+        <v>603</v>
+      </c>
+      <c r="N86" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A87" s="33">
+        <v>36</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="38"/>
+      <c r="D87" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="F87" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G84" s="16" t="s">
+      <c r="G87" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H84" s="20">
-        <v>43180</v>
-      </c>
-      <c r="I84" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J84" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K84" s="20">
+      <c r="H87" s="50">
+        <v>43647</v>
+      </c>
+      <c r="I87" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="43">
+        <v>45173</v>
+      </c>
+      <c r="L87" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="M87" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="N87" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A88" s="33">
+        <v>37</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="38"/>
+      <c r="D88" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="E88" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H88" s="50">
+        <v>43452</v>
+      </c>
+      <c r="I88" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="50">
+        <v>45145</v>
+      </c>
+      <c r="L88" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="M88" s="33" t="s">
+        <v>624</v>
+      </c>
+      <c r="N88" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A89" s="33">
+        <v>38</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="38"/>
+      <c r="D89" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="E89" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="F89" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H89" s="50">
+        <v>43650</v>
+      </c>
+      <c r="I89" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L89" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="M89" s="33" t="s">
+        <v>609</v>
+      </c>
+      <c r="N89" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A90" s="33">
+        <v>39</v>
+      </c>
+      <c r="B90" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="38"/>
+      <c r="D90" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="F90" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H90" s="50">
+        <v>43384</v>
+      </c>
+      <c r="I90" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90" s="50">
+        <v>44775</v>
+      </c>
+      <c r="L90" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="M90" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="N90" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A91" s="33">
+        <v>40</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="38"/>
+      <c r="D91" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="E91" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="F91" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H91" s="50">
+        <v>43556</v>
+      </c>
+      <c r="I91" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L91" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="M91" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="N91" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A92" s="33">
+        <v>41</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="38"/>
+      <c r="D92" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="E92" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F92" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H92" s="50">
+        <v>43593</v>
+      </c>
+      <c r="I92" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L92" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="M92" s="33" t="s">
+        <v>609</v>
+      </c>
+      <c r="N92" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A93" s="33">
+        <v>42</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="38"/>
+      <c r="D93" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E93" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F93" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H93" s="50">
+        <v>43691</v>
+      </c>
+      <c r="I93" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K93" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L93" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="M93" s="33"/>
+      <c r="N93" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A94" s="33">
+        <v>43</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="38"/>
+      <c r="D94" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="E94" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="F94" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H94" s="50">
+        <v>43790</v>
+      </c>
+      <c r="I94" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="50">
         <v>45166</v>
       </c>
-      <c r="L84" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="M84" s="25" t="s">
-        <v>703</v>
-      </c>
-      <c r="N84" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="15.75">
-      <c r="A85" s="16">
-        <v>34</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F85" s="16" t="s">
+      <c r="L94" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="M94" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="N94" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A95" s="33">
+        <v>44</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="38"/>
+      <c r="D95" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G95" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H85" s="20">
-        <v>44000</v>
-      </c>
-      <c r="I85" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J85" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K85" s="20">
-        <v>45139</v>
-      </c>
-      <c r="L85" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="M85" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="N85" s="16" t="s">
+      <c r="H95" s="50">
+        <v>43511</v>
+      </c>
+      <c r="I95" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K95" s="50">
+        <v>45167</v>
+      </c>
+      <c r="L95" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="M95" s="33"/>
+      <c r="N95" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A96" s="33">
+        <v>45</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="38"/>
+      <c r="D96" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="E96" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="F96" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="H96" s="50">
+        <v>43472</v>
+      </c>
+      <c r="I96" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K96" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L96" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="M96" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N96" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15.75">
-      <c r="A86" s="16">
-        <v>35</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="18"/>
-      <c r="D86" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F86" s="16" t="s">
+    <row r="97" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A97" s="33">
+        <v>46</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="38"/>
+      <c r="D97" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="E97" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F97" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G97" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H86" s="20">
-        <v>44174</v>
-      </c>
-      <c r="I86" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J86" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K86" s="20">
-        <v>45173</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="M86" s="16" t="s">
-        <v>603</v>
-      </c>
-      <c r="N86" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="15.75">
-      <c r="A87" s="16">
-        <v>36</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="F87" s="16" t="s">
+      <c r="H97" s="50">
+        <v>43183</v>
+      </c>
+      <c r="I97" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K97" s="50">
+        <v>45140</v>
+      </c>
+      <c r="L97" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="M97" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N97" s="39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="51" customFormat="1" ht="15.75">
+      <c r="A98" s="33">
+        <v>47</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="38"/>
+      <c r="D98" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="E98" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F98" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G87" s="16" t="s">
+      <c r="G98" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="H87" s="20">
-        <v>43647</v>
-      </c>
-      <c r="I87" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K87" s="20"/>
-      <c r="L87" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="M87" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="N87" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="15.75">
-      <c r="A88" s="16">
-        <v>37</v>
-      </c>
-      <c r="B88" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="18"/>
-      <c r="D88" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="E88" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="F88" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H88" s="20">
-        <v>43452</v>
-      </c>
-      <c r="I88" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J88" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K88" s="20">
+      <c r="H98" s="50">
+        <v>43302</v>
+      </c>
+      <c r="I98" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K98" s="50">
         <v>45145</v>
       </c>
-      <c r="L88" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="M88" s="16" t="s">
-        <v>624</v>
-      </c>
-      <c r="N88" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="15.75">
-      <c r="A89" s="16">
-        <v>38</v>
-      </c>
-      <c r="B89" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89" s="18"/>
-      <c r="D89" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F89" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H89" s="20">
-        <v>43650</v>
-      </c>
-      <c r="I89" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J89" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K89" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="M89" s="16" t="s">
-        <v>609</v>
-      </c>
-      <c r="N89" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="15.75">
-      <c r="A90" s="16">
-        <v>39</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C90" s="18"/>
-      <c r="D90" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="E90" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H90" s="20">
-        <v>43384</v>
-      </c>
-      <c r="I90" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J90" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K90" s="20">
-        <v>44775</v>
-      </c>
-      <c r="L90" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="M90" s="16" t="s">
-        <v>625</v>
-      </c>
-      <c r="N90" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="15.75">
-      <c r="A91" s="16">
-        <v>40</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="18"/>
-      <c r="D91" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E91" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="F91" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H91" s="20">
-        <v>43556</v>
-      </c>
-      <c r="I91" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J91" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K91" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L91" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="M91" s="16" t="s">
-        <v>626</v>
-      </c>
-      <c r="N91" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="15.75">
-      <c r="A92" s="16">
-        <v>41</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" s="18"/>
-      <c r="D92" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H92" s="20">
-        <v>43593</v>
-      </c>
-      <c r="I92" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J92" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K92" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L92" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="M92" s="16" t="s">
-        <v>609</v>
-      </c>
-      <c r="N92" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="15.75">
-      <c r="A93" s="16">
-        <v>42</v>
-      </c>
-      <c r="B93" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C93" s="19"/>
-      <c r="D93" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="E93" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="F93" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H93" s="20">
-        <v>43691</v>
-      </c>
-      <c r="I93" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J93" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K93" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L93" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="M93" s="16" t="s">
-        <v>627</v>
-      </c>
-      <c r="N93" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="15.75">
-      <c r="A94" s="16">
-        <v>43</v>
-      </c>
-      <c r="B94" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C94" s="19"/>
-      <c r="D94" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="E94" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="F94" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G94" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H94" s="20">
-        <v>43790</v>
-      </c>
-      <c r="I94" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J94" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K94" s="20">
-        <v>45166</v>
-      </c>
-      <c r="L94" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="M94" s="16" t="s">
-        <v>628</v>
-      </c>
-      <c r="N94" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="15.75">
-      <c r="A95" s="16">
-        <v>44</v>
-      </c>
-      <c r="B95" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C95" s="19"/>
-      <c r="D95" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H95" s="20">
-        <v>43511</v>
-      </c>
-      <c r="I95" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J95" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K95" s="20">
-        <v>45167</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="M95" s="16"/>
-      <c r="N95" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="15.75">
-      <c r="A96" s="16">
-        <v>45</v>
-      </c>
-      <c r="B96" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C96" s="19"/>
-      <c r="D96" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H96" s="20">
-        <v>43472</v>
-      </c>
-      <c r="I96" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J96" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K96" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="M96" s="16" t="s">
-        <v>629</v>
-      </c>
-      <c r="N96" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="15.75">
-      <c r="A97" s="16">
-        <v>46</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" s="19"/>
-      <c r="D97" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="E97" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="F97" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H97" s="20">
-        <v>43183</v>
-      </c>
-      <c r="I97" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J97" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K97" s="20">
-        <v>45140</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="M97" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="N97" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="15.75">
-      <c r="A98" s="16">
-        <v>47</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C98" s="19"/>
-      <c r="D98" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H98" s="20">
-        <v>43302</v>
-      </c>
-      <c r="I98" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J98" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="K98" s="20">
-        <v>45145</v>
-      </c>
-      <c r="L98" s="7" t="s">
+      <c r="L98" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="M98" s="16" t="s">
+      <c r="M98" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="N98" s="16" t="s">
+      <c r="N98" s="33" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7515,7 +7514,7 @@
         <v>253</v>
       </c>
       <c r="M100" s="16" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="N100" s="7" t="s">
         <v>21</v>
@@ -7557,7 +7556,7 @@
         <v>256</v>
       </c>
       <c r="M101" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N101" s="7" t="s">
         <v>21</v>
@@ -7599,7 +7598,7 @@
         <v>259</v>
       </c>
       <c r="M102" s="16" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N102" s="16" t="s">
         <v>57</v>
@@ -7683,7 +7682,7 @@
         <v>66</v>
       </c>
       <c r="M104" s="16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="N104" s="16" t="s">
         <v>57</v>
@@ -7725,7 +7724,7 @@
         <v>265</v>
       </c>
       <c r="M105" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N105" s="7" t="s">
         <v>21</v>
@@ -7851,7 +7850,7 @@
         <v>208</v>
       </c>
       <c r="M108" s="16" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N108" s="7" t="s">
         <v>21</v>
@@ -7893,7 +7892,7 @@
         <v>273</v>
       </c>
       <c r="M109" s="24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N109" s="7" t="s">
         <v>21</v>
@@ -7928,10 +7927,10 @@
       </c>
       <c r="K110" s="20"/>
       <c r="L110" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M110" s="24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N110" s="7" t="s">
         <v>21</v>
@@ -7973,7 +7972,7 @@
       </c>
       <c r="L111" s="7"/>
       <c r="M111" s="24" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="N111" s="7" t="s">
         <v>21</v>
@@ -8012,10 +8011,10 @@
         <v>45240</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M112" s="24" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N112" s="7" t="s">
         <v>21</v>
@@ -8057,7 +8056,7 @@
         <v>215</v>
       </c>
       <c r="M113" s="24" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N113" s="16" t="s">
         <v>57</v>
@@ -8099,7 +8098,7 @@
         <v>69</v>
       </c>
       <c r="M114" s="24" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N114" s="7" t="s">
         <v>57</v>
@@ -8217,7 +8216,7 @@
         <v>284</v>
       </c>
       <c r="M117" s="16" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="N117" s="7" t="s">
         <v>57</v>
@@ -8341,7 +8340,7 @@
         <v>294</v>
       </c>
       <c r="M120" s="24" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="N120" s="7" t="s">
         <v>21</v>
@@ -8383,7 +8382,7 @@
         <v>297</v>
       </c>
       <c r="M121" s="24" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N121" s="7" t="s">
         <v>21</v>
@@ -8425,7 +8424,7 @@
         <v>300</v>
       </c>
       <c r="M122" s="24" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N122" s="16" t="s">
         <v>57</v>
@@ -8467,7 +8466,7 @@
         <v>303</v>
       </c>
       <c r="M123" s="24" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N123" s="16" t="s">
         <v>57</v>
@@ -8507,7 +8506,7 @@
       </c>
       <c r="L124" s="7"/>
       <c r="M124" s="24" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N124" s="7" t="s">
         <v>21</v>
@@ -8549,7 +8548,7 @@
         <v>307</v>
       </c>
       <c r="M125" s="24" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N125" s="16" t="s">
         <v>57</v>
@@ -8591,7 +8590,7 @@
         <v>300</v>
       </c>
       <c r="M126" s="24" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N126" s="16" t="s">
         <v>57</v>
@@ -8673,7 +8672,7 @@
         <v>313</v>
       </c>
       <c r="M128" s="24" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N128" s="7" t="s">
         <v>21</v>
@@ -8715,7 +8714,7 @@
         <v>316</v>
       </c>
       <c r="M129" s="16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>57</v>
@@ -8793,7 +8792,7 @@
         <v>259</v>
       </c>
       <c r="M131" s="24" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N131" s="16" t="s">
         <v>57</v>
@@ -8877,7 +8876,7 @@
         <v>323</v>
       </c>
       <c r="M133" s="31" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="N133" s="16" t="s">
         <v>57</v>
@@ -8919,7 +8918,7 @@
         <v>326</v>
       </c>
       <c r="M134" s="31" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="N134" s="7" t="s">
         <v>21</v>
@@ -8961,7 +8960,7 @@
         <v>329</v>
       </c>
       <c r="M135" s="24" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N135" s="7" t="s">
         <v>21</v>
@@ -9001,7 +9000,7 @@
         <v>332</v>
       </c>
       <c r="M136" s="24" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N136" s="7" t="s">
         <v>21</v>
@@ -9207,7 +9206,7 @@
         <v>341</v>
       </c>
       <c r="M141" s="24" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N141" s="7" t="s">
         <v>57</v>
@@ -9249,7 +9248,7 @@
         <v>344</v>
       </c>
       <c r="M142" s="24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N142" s="7" t="s">
         <v>21</v>
@@ -9291,7 +9290,7 @@
         <v>303</v>
       </c>
       <c r="M143" s="24" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N143" s="16" t="s">
         <v>57</v>
@@ -9333,7 +9332,7 @@
         <v>347</v>
       </c>
       <c r="M144" s="24" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="N144" s="7" t="s">
         <v>21</v>
@@ -9415,7 +9414,7 @@
         <v>307</v>
       </c>
       <c r="M146" s="24" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N146" s="16" t="s">
         <v>57</v>
@@ -9457,7 +9456,7 @@
         <v>244</v>
       </c>
       <c r="M147" s="24" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="N147" s="16" t="s">
         <v>57</v>
@@ -9499,7 +9498,7 @@
         <v>355</v>
       </c>
       <c r="M148" s="24" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N148" s="7" t="s">
         <v>21</v>
@@ -9541,7 +9540,7 @@
         <v>358</v>
       </c>
       <c r="M149" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N149" s="7" t="s">
         <v>21</v>
@@ -9583,7 +9582,7 @@
         <v>361</v>
       </c>
       <c r="M150" s="24" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="N150" s="7" t="s">
         <v>21</v>
@@ -9625,7 +9624,7 @@
         <v>323</v>
       </c>
       <c r="M151" s="24" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="N151" s="16" t="s">
         <v>57</v>
@@ -9707,7 +9706,7 @@
         <v>366</v>
       </c>
       <c r="M153" s="31" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N153" s="16" t="s">
         <v>57</v>
@@ -9747,7 +9746,7 @@
         <v>369</v>
       </c>
       <c r="M154" s="24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N154" s="7" t="s">
         <v>21</v>
@@ -9827,7 +9826,7 @@
         <v>374</v>
       </c>
       <c r="M156" s="24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="N156" s="7" t="s">
         <v>21</v>
@@ -9989,7 +9988,7 @@
         <v>383</v>
       </c>
       <c r="M160" s="16" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N160" s="16" t="s">
         <v>57</v>
@@ -10031,7 +10030,7 @@
         <v>385</v>
       </c>
       <c r="M161" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N161" s="7" t="s">
         <v>57</v>
@@ -10046,7 +10045,7 @@
       </c>
       <c r="C162" s="19"/>
       <c r="D162" s="14" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E162" s="15" t="s">
         <v>386</v>
@@ -10070,10 +10069,10 @@
         <v>45523</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="M162" s="16" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N162" s="7" t="s">
         <v>21</v>
@@ -10115,7 +10114,7 @@
         <v>389</v>
       </c>
       <c r="M163" s="24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N163" s="7" t="s">
         <v>21</v>
@@ -10157,7 +10156,7 @@
         <v>392</v>
       </c>
       <c r="M164" s="24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="N164" s="7" t="s">
         <v>21</v>
@@ -10177,7 +10176,7 @@
         <v>393</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F165" s="16" t="s">
         <v>17</v>
@@ -10198,10 +10197,10 @@
         <v>45223</v>
       </c>
       <c r="L165" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="M165" s="16" t="s">
         <v>639</v>
-      </c>
-      <c r="M165" s="16" t="s">
-        <v>640</v>
       </c>
       <c r="N165" s="7" t="s">
         <v>21</v>
@@ -10221,7 +10220,7 @@
         <v>395</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F166" s="16" t="s">
         <v>17</v>
@@ -10245,7 +10244,7 @@
         <v>152</v>
       </c>
       <c r="M166" s="29" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="N166" s="7" t="s">
         <v>21</v>
@@ -10262,7 +10261,7 @@
         <v>523</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E167" s="15" t="s">
         <v>360</v>
@@ -10287,7 +10286,7 @@
       </c>
       <c r="L167" s="7"/>
       <c r="M167" s="31" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="N167" s="7" t="s">
         <v>21</v>
@@ -10304,10 +10303,10 @@
         <v>668</v>
       </c>
       <c r="D168" s="14" t="s">
+        <v>697</v>
+      </c>
+      <c r="E168" s="15" t="s">
         <v>698</v>
-      </c>
-      <c r="E168" s="15" t="s">
-        <v>699</v>
       </c>
       <c r="F168" s="16" t="s">
         <v>17</v>
@@ -10328,10 +10327,10 @@
         <v>45024</v>
       </c>
       <c r="L168" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="M168" s="16" t="s">
         <v>641</v>
-      </c>
-      <c r="M168" s="16" t="s">
-        <v>642</v>
       </c>
       <c r="N168" s="7" t="s">
         <v>57</v>
@@ -10416,10 +10415,10 @@
         <v>45140</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M170" s="31" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="N170" s="7" t="s">
         <v>21</v>
@@ -10463,7 +10462,7 @@
         <v>284</v>
       </c>
       <c r="M171" s="16" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="N171" s="7" t="s">
         <v>57</v>
@@ -10548,10 +10547,10 @@
         <v>45223</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M173" s="31" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N173" s="7" t="s">
         <v>21</v>
@@ -10636,10 +10635,10 @@
         <v>45140</v>
       </c>
       <c r="L175" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="M175" s="16" t="s">
         <v>644</v>
-      </c>
-      <c r="M175" s="16" t="s">
-        <v>645</v>
       </c>
       <c r="N175" s="7" t="s">
         <v>21</v>
@@ -10683,7 +10682,7 @@
         <v>101</v>
       </c>
       <c r="M176" s="16" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N176" s="7" t="s">
         <v>57</v>
@@ -10771,7 +10770,7 @@
         <v>316</v>
       </c>
       <c r="M178" s="16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="N178" s="16" t="s">
         <v>57</v>
@@ -10815,7 +10814,7 @@
         <v>383</v>
       </c>
       <c r="M179" s="16" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N179" s="16" t="s">
         <v>57</v>
@@ -10832,7 +10831,7 @@
         <v>522</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E180" s="15" t="s">
         <v>405</v>
@@ -10856,10 +10855,10 @@
         <v>44440</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M180" s="32" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N180" s="7" t="s">
         <v>21</v>
@@ -10900,7 +10899,7 @@
         <v>45146</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M181" s="32" t="s">
         <v>609</v>
@@ -10944,10 +10943,10 @@
         <v>45139</v>
       </c>
       <c r="L182" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="M182" s="16" t="s">
         <v>650</v>
-      </c>
-      <c r="M182" s="16" t="s">
-        <v>651</v>
       </c>
       <c r="N182" s="7" t="s">
         <v>21</v>
@@ -10988,7 +10987,7 @@
         <v>45140</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="M183" s="32" t="s">
         <v>624</v>
@@ -11032,10 +11031,10 @@
         <v>45303</v>
       </c>
       <c r="L184" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="M184" s="29" t="s">
         <v>733</v>
-      </c>
-      <c r="M184" s="29" t="s">
-        <v>734</v>
       </c>
       <c r="N184" s="7" t="s">
         <v>21</v>
@@ -11076,10 +11075,10 @@
         <v>45139</v>
       </c>
       <c r="L185" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="M185" s="16" t="s">
         <v>652</v>
-      </c>
-      <c r="M185" s="16" t="s">
-        <v>653</v>
       </c>
       <c r="N185" s="7" t="s">
         <v>57</v>
@@ -11099,7 +11098,7 @@
         <v>411</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F186" s="16" t="s">
         <v>17</v>
@@ -11120,10 +11119,10 @@
         <v>45140</v>
       </c>
       <c r="L186" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="M186" s="16" t="s">
         <v>654</v>
-      </c>
-      <c r="M186" s="16" t="s">
-        <v>655</v>
       </c>
       <c r="N186" s="7" t="s">
         <v>21</v>
@@ -11160,10 +11159,10 @@
       </c>
       <c r="K187" s="20"/>
       <c r="L187" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="M187" s="16" t="s">
         <v>656</v>
-      </c>
-      <c r="M187" s="16" t="s">
-        <v>657</v>
       </c>
       <c r="N187" s="7" t="s">
         <v>57</v>
@@ -11200,10 +11199,10 @@
       </c>
       <c r="K188" s="20"/>
       <c r="L188" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="M188" s="16" t="s">
         <v>656</v>
-      </c>
-      <c r="M188" s="16" t="s">
-        <v>657</v>
       </c>
       <c r="N188" s="7" t="s">
         <v>57</v>
@@ -11221,7 +11220,7 @@
         <v>414</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F189" s="16" t="s">
         <v>17</v>
@@ -11239,7 +11238,7 @@
       <c r="K189" s="20"/>
       <c r="L189" s="7"/>
       <c r="M189" s="29" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="N189" s="7" t="s">
         <v>21</v>
@@ -11279,7 +11278,7 @@
         <v>385</v>
       </c>
       <c r="M190" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N190" s="7" t="s">
         <v>57</v>
@@ -11320,10 +11319,10 @@
         <v>45627</v>
       </c>
       <c r="L191" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="M191" s="16" t="s">
         <v>660</v>
-      </c>
-      <c r="M191" s="16" t="s">
-        <v>661</v>
       </c>
       <c r="N191" s="7" t="s">
         <v>21</v>
@@ -11367,7 +11366,7 @@
         <v>416</v>
       </c>
       <c r="M192" s="31" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="N192" s="7" t="s">
         <v>57</v>
@@ -11452,10 +11451,10 @@
         <v>45139</v>
       </c>
       <c r="L194" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="M194" s="16" t="s">
         <v>662</v>
-      </c>
-      <c r="M194" s="16" t="s">
-        <v>663</v>
       </c>
       <c r="N194" s="7" t="s">
         <v>57</v>
@@ -11496,10 +11495,10 @@
         <v>45142</v>
       </c>
       <c r="L195" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="M195" s="16" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N195" s="7" t="s">
         <v>57</v>
@@ -11540,10 +11539,10 @@
         <v>45148</v>
       </c>
       <c r="L196" s="7" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M196" s="31" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="N196" s="7" t="s">
         <v>21</v>
@@ -11584,10 +11583,10 @@
         <v>45140</v>
       </c>
       <c r="L197" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M197" s="31" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="N197" s="7" t="s">
         <v>21</v>
@@ -11628,10 +11627,10 @@
         <v>45148</v>
       </c>
       <c r="L198" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M198" s="31" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="N198" s="7" t="s">
         <v>21</v>
@@ -11672,7 +11671,7 @@
         <v>45140</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M199" s="16" t="s">
         <v>566</v>
@@ -11716,7 +11715,7 @@
         <v>45140</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="M200" s="16"/>
       <c r="N200" s="7" t="s">
@@ -11758,10 +11757,10 @@
         <v>45223</v>
       </c>
       <c r="L201" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="M201" s="29" t="s">
         <v>737</v>
-      </c>
-      <c r="M201" s="29" t="s">
-        <v>738</v>
       </c>
       <c r="N201" s="7" t="s">
         <v>57</v>
@@ -11802,10 +11801,10 @@
         <v>45223</v>
       </c>
       <c r="L202" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M202" s="31" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="N202" s="7" t="s">
         <v>57</v>
@@ -11846,10 +11845,10 @@
         <v>45139</v>
       </c>
       <c r="L203" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="M203" s="16" t="s">
         <v>666</v>
-      </c>
-      <c r="M203" s="16" t="s">
-        <v>667</v>
       </c>
       <c r="N203" s="7" t="s">
         <v>21</v>
@@ -11890,7 +11889,7 @@
         <v>45148</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M204" s="31" t="s">
         <v>612</v>
@@ -11937,7 +11936,7 @@
         <v>599</v>
       </c>
       <c r="M205" s="28" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="N205" s="7" t="s">
         <v>21</v>
@@ -12025,7 +12024,7 @@
         <v>436</v>
       </c>
       <c r="M207" s="31" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="N207" s="7" t="s">
         <v>21</v>
@@ -12066,10 +12065,10 @@
         <v>45145</v>
       </c>
       <c r="L208" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="M208" s="29" t="s">
         <v>740</v>
-      </c>
-      <c r="M208" s="29" t="s">
-        <v>741</v>
       </c>
       <c r="N208" s="7" t="s">
         <v>21</v>
@@ -12110,10 +12109,10 @@
         <v>45140</v>
       </c>
       <c r="L209" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="M209" s="29" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N209" s="7" t="s">
         <v>21</v>
@@ -12154,10 +12153,10 @@
         <v>45303</v>
       </c>
       <c r="L210" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="M210" s="29" t="s">
         <v>746</v>
-      </c>
-      <c r="M210" s="29" t="s">
-        <v>747</v>
       </c>
       <c r="N210" s="7" t="s">
         <v>21</v>
@@ -12198,10 +12197,10 @@
         <v>45153</v>
       </c>
       <c r="L211" s="7" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="M211" s="31" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="N211" s="7" t="s">
         <v>21</v>
@@ -12242,10 +12241,10 @@
         <v>45142</v>
       </c>
       <c r="L212" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M212" s="31" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N212" s="7" t="s">
         <v>21</v>
@@ -12286,7 +12285,7 @@
         <v>45142</v>
       </c>
       <c r="L213" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M213" s="16"/>
       <c r="N213" s="7" t="s">
@@ -12328,10 +12327,10 @@
         <v>45146</v>
       </c>
       <c r="L214" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="M214" s="29" t="s">
         <v>746</v>
-      </c>
-      <c r="M214" s="29" t="s">
-        <v>747</v>
       </c>
       <c r="N214" s="7" t="s">
         <v>21</v>
@@ -12372,10 +12371,10 @@
         <v>45302</v>
       </c>
       <c r="L215" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="M215" s="31" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="N215" s="7" t="s">
         <v>21</v>
@@ -12455,7 +12454,7 @@
       </c>
       <c r="L217" s="7"/>
       <c r="M217" s="31" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="N217" s="7" t="s">
         <v>21</v>
@@ -12499,7 +12498,7 @@
         <v>358</v>
       </c>
       <c r="M218" s="24" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N218" s="7" t="s">
         <v>21</v>
@@ -12628,10 +12627,10 @@
         <v>44445</v>
       </c>
       <c r="L221" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M221" s="31" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="N221" s="7" t="s">
         <v>21</v>
@@ -12672,10 +12671,10 @@
         <v>44823</v>
       </c>
       <c r="L222" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="M222" s="29" t="s">
         <v>737</v>
-      </c>
-      <c r="M222" s="29" t="s">
-        <v>738</v>
       </c>
       <c r="N222" s="7" t="s">
         <v>21</v>
@@ -12760,10 +12759,10 @@
         <v>44783</v>
       </c>
       <c r="L224" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="M224" s="32" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N224" s="7" t="s">
         <v>21</v>
@@ -12807,7 +12806,7 @@
         <v>366</v>
       </c>
       <c r="M225" s="31" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N225" s="7" t="s">
         <v>57</v>
@@ -12848,7 +12847,7 @@
         <v>45148</v>
       </c>
       <c r="L226" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="M226" s="16"/>
       <c r="N226" s="7" t="s">
@@ -12890,10 +12889,10 @@
         <v>44236</v>
       </c>
       <c r="L227" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M227" s="31" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N227" s="7" t="s">
         <v>21</v>
@@ -12934,7 +12933,7 @@
         <v>45207</v>
       </c>
       <c r="L228" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="M228" s="16"/>
       <c r="N228" s="7" t="s">
@@ -12976,10 +12975,10 @@
         <v>44124</v>
       </c>
       <c r="L229" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="M229" s="31" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="N229" s="7" t="s">
         <v>21</v>
@@ -13067,7 +13066,7 @@
         <v>341</v>
       </c>
       <c r="M231" s="24" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N231" s="7" t="s">
         <v>57</v>
@@ -13192,10 +13191,10 @@
         <v>45223</v>
       </c>
       <c r="L234" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M234" s="31" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N234" s="7" t="s">
         <v>21</v>
@@ -13236,10 +13235,10 @@
         <v>44842</v>
       </c>
       <c r="L235" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="M235" s="31" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="N235" s="7" t="s">
         <v>21</v>
@@ -13280,10 +13279,10 @@
         <v>44783</v>
       </c>
       <c r="L236" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="M236" s="31" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="N236" s="7" t="s">
         <v>21</v>
@@ -13324,10 +13323,10 @@
         <v>44842</v>
       </c>
       <c r="L237" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="M237" s="16" t="s">
         <v>662</v>
-      </c>
-      <c r="M237" s="16" t="s">
-        <v>663</v>
       </c>
       <c r="N237" s="7" t="s">
         <v>57</v>
@@ -13368,10 +13367,10 @@
         <v>44124</v>
       </c>
       <c r="L238" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="M238" s="31" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="N238" s="7" t="s">
         <v>21</v>
@@ -13412,10 +13411,10 @@
         <v>44779</v>
       </c>
       <c r="L239" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M239" s="31" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="N239" s="7" t="s">
         <v>21</v>
@@ -13456,10 +13455,10 @@
         <v>45207</v>
       </c>
       <c r="L240" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M240" s="31" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N240" s="7" t="s">
         <v>21</v>
@@ -13500,10 +13499,10 @@
         <v>45207</v>
       </c>
       <c r="L241" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M241" s="31" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="N241" s="7" t="s">
         <v>21</v>
@@ -13520,7 +13519,7 @@
         <v>546</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E242" s="15" t="s">
         <v>164</v>
@@ -13544,10 +13543,10 @@
         <v>44445</v>
       </c>
       <c r="L242" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="M242" s="32" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N242" s="7" t="s">
         <v>21</v>
@@ -13584,10 +13583,10 @@
       </c>
       <c r="K243" s="20"/>
       <c r="L243" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="M243" s="31" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N243" s="7" t="s">
         <v>21</v>
@@ -13624,10 +13623,10 @@
       </c>
       <c r="K244" s="20"/>
       <c r="L244" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="M244" s="31" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N244" s="7" t="s">
         <v>21</v>
@@ -13746,10 +13745,10 @@
         <v>45252</v>
       </c>
       <c r="L247" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="M247" s="31" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="N247" s="7" t="s">
         <v>21</v>
@@ -13790,10 +13789,10 @@
         <v>44777</v>
       </c>
       <c r="L248" s="7" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M248" s="32" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N248" s="7" t="s">
         <v>21</v>
@@ -13834,10 +13833,10 @@
         <v>44783</v>
       </c>
       <c r="L249" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="M249" s="31" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N249" s="7" t="s">
         <v>21</v>
@@ -13878,10 +13877,10 @@
         <v>44778</v>
       </c>
       <c r="L250" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="M250" s="32" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="N250" s="7" t="s">
         <v>21</v>
@@ -13922,10 +13921,10 @@
         <v>44778</v>
       </c>
       <c r="L251" s="7" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="M251" s="31" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="N251" s="7" t="s">
         <v>21</v>
@@ -13969,7 +13968,7 @@
         <v>294</v>
       </c>
       <c r="M252" s="24" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="N252" s="7" t="s">
         <v>57</v>
@@ -14010,10 +14009,10 @@
         <v>44443</v>
       </c>
       <c r="L253" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M253" s="32" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="N253" s="7" t="s">
         <v>21</v>
@@ -14054,10 +14053,10 @@
         <v>44783</v>
       </c>
       <c r="L254" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="M254" s="16" t="s">
         <v>652</v>
-      </c>
-      <c r="M254" s="16" t="s">
-        <v>653</v>
       </c>
       <c r="N254" s="7" t="s">
         <v>57</v>
@@ -14099,7 +14098,7 @@
       </c>
       <c r="L255" s="7"/>
       <c r="M255" s="32" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="N255" s="7" t="s">
         <v>21</v>
@@ -14183,7 +14182,7 @@
         <v>265</v>
       </c>
       <c r="M257" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N257" s="7" t="s">
         <v>21</v>
@@ -14225,7 +14224,7 @@
         <v>344</v>
       </c>
       <c r="M258" s="31" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="N258" s="7" t="s">
         <v>21</v>
@@ -14264,7 +14263,7 @@
         <v>45148</v>
       </c>
       <c r="L259" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="M259" s="16"/>
       <c r="N259" s="7" t="s">
@@ -14302,10 +14301,10 @@
       </c>
       <c r="K260" s="20"/>
       <c r="L260" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="M260" s="31" t="s">
         <v>764</v>
-      </c>
-      <c r="M260" s="31" t="s">
-        <v>765</v>
       </c>
       <c r="N260" s="7" t="s">
         <v>21</v>
@@ -14342,10 +14341,10 @@
       </c>
       <c r="K261" s="20"/>
       <c r="L261" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="M261" s="31" t="s">
         <v>766</v>
-      </c>
-      <c r="M261" s="31" t="s">
-        <v>767</v>
       </c>
       <c r="N261" s="7" t="s">
         <v>21</v>
@@ -14385,10 +14384,10 @@
         <v>45139</v>
       </c>
       <c r="L262" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="M262" s="31" t="s">
         <v>666</v>
-      </c>
-      <c r="M262" s="31" t="s">
-        <v>667</v>
       </c>
       <c r="N262" s="7" t="s">
         <v>21</v>
@@ -14425,10 +14424,10 @@
       </c>
       <c r="K263" s="20"/>
       <c r="L263" s="7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="M263" s="31" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="N263" s="7" t="s">
         <v>21</v>
@@ -14625,10 +14624,10 @@
       </c>
       <c r="K268" s="20"/>
       <c r="L268" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="M268" s="31" t="s">
         <v>761</v>
-      </c>
-      <c r="M268" s="31" t="s">
-        <v>762</v>
       </c>
       <c r="N268" s="7" t="s">
         <v>21</v>

--- a/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CADF019-7EE1-4ED5-B227-B523C8AAA8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911DDC21-6708-4FAE-AFB4-C1E955815894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Record" sheetId="1" r:id="rId1"/>

--- a/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
+++ b/Sindhi Muslim/Classes/GBPS Sindhi Jamaat Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911DDC21-6708-4FAE-AFB4-C1E955815894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA48735A-DE86-43C5-84C1-5F442E5FAEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Record" sheetId="1" r:id="rId1"/>
